--- a/output/daily_ratings/france_ratings_2026-03-22.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-22.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P2" t="n">
-        <v>102.7313641558257</v>
+        <v>103.6675058039727</v>
       </c>
       <c r="Q2" t="n">
         <v>1.867959999999982</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.22340242066748</v>
+        <v>69.7101969982551</v>
       </c>
       <c r="T2" t="n">
-        <v>85.22340242066748</v>
+        <v>69.7101969982551</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P3" t="n">
-        <v>102.6454517760143</v>
+        <v>103.581390840231</v>
       </c>
       <c r="Q3" t="n">
         <v>4.072579999999988</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>86.68473520603136</v>
+        <v>71.17436623809165</v>
       </c>
       <c r="T3" t="n">
-        <v>86.68473520603136</v>
+        <v>71.17436623809165</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>0.53</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P4" t="n">
-        <v>101.2135787791562</v>
+        <v>102.1461414445354</v>
       </c>
       <c r="Q4" t="n">
         <v>1.867959999999982</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>84.17654276389437</v>
+        <v>68.65873152635513</v>
       </c>
       <c r="T4" t="n">
-        <v>84.17654276389437</v>
+        <v>68.65873152635513</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P5" t="n">
-        <v>97.63389628701087</v>
+        <v>98.55801795529644</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.3366600000000091</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>80.18694514707845</v>
+        <v>64.65517397702432</v>
       </c>
       <c r="T5" t="n">
-        <v>80.18694514707845</v>
+        <v>64.65517397702432</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>1.81</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P6" t="n">
-        <v>97.54798390719938</v>
+        <v>98.4719029915547</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>77.84680545156475</v>
+        <v>62.31012783351007</v>
       </c>
       <c r="T6" t="n">
-        <v>77.84680545156475</v>
+        <v>62.31012783351007</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P7" t="n">
-        <v>97.46207152738789</v>
+        <v>98.38578802781296</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>83.86990521398168</v>
+        <v>68.34535553336758</v>
       </c>
       <c r="T7" t="n">
-        <v>83.86990521398168</v>
+        <v>68.34535553336758</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.34</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P8" t="n">
-        <v>90.30270654309733</v>
+        <v>91.20954104933509</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.3366600000000091</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>75.13041548417432</v>
+        <v>59.57639735803581</v>
       </c>
       <c r="T8" t="n">
-        <v>75.13041548417432</v>
+        <v>59.57639735803581</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.34</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P9" t="n">
-        <v>87.43896054938111</v>
+        <v>88.33904225794393</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.3366600000000091</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>73.15520858460239</v>
+        <v>57.59250024124342</v>
       </c>
       <c r="T9" t="n">
-        <v>73.15520858460239</v>
+        <v>57.59250024124342</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.59</v>
       </c>
       <c r="O10" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P10" t="n">
-        <v>83.85927805723583</v>
+        <v>84.75091876870499</v>
       </c>
       <c r="Q10" t="n">
         <v>-4.745900000000006</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>67.64502197543543</v>
+        <v>52.06525653857229</v>
       </c>
       <c r="T10" t="n">
-        <v>67.64502197543543</v>
+        <v>52.06525653857229</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.84</v>
       </c>
       <c r="O11" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P11" t="n">
-        <v>83.14334155880677</v>
+        <v>84.03329407085721</v>
       </c>
       <c r="Q11" t="n">
         <v>4.072579999999988</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>73.23357621994656</v>
+        <v>57.66402687273549</v>
       </c>
       <c r="T11" t="n">
-        <v>73.23357621994656</v>
+        <v>57.66402687273549</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>7.09</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000290627244169187</v>
+        <v>0.0003145748770905718</v>
       </c>
       <c r="P12" t="n">
-        <v>82.42740506037771</v>
+        <v>83.31566937300941</v>
       </c>
       <c r="Q12" t="n">
         <v>2.970269999999999</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>71.97947999887808</v>
+        <v>56.40620951686724</v>
       </c>
       <c r="T12" t="n">
-        <v>71.97947999887808</v>
+        <v>56.40620951686724</v>
       </c>
     </row>
     <row r="13">
@@ -1392,23 +1392,17 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-401.8439149401822</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
-        <v>-265.7554385550005</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-265.7554385550005</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1466,23 +1460,17 @@
         <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-407.1692152117222</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>4.072579999999988</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="n">
-        <v>-264.8666823343897</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-264.8666823343897</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1540,23 +1528,17 @@
         <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-407.7017452388762</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="n">
-        <v>-269.795750387087</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-269.795750387087</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1614,23 +1596,17 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-408.2342752660302</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="n">
-        <v>-267.1218734780292</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-267.1218734780292</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1688,23 +1664,17 @@
         <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-409.2993353203382</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
         <v>2.970269999999999</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="n">
-        <v>-267.0961811331421</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-267.0961811331421</v>
-      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1762,23 +1732,17 @@
         <v>3.53</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-409.3632389235967</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
         <v>-6.950520000000012</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="n">
-        <v>-273.982907727799</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-273.982907727799</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1836,23 +1800,17 @@
         <v>4.779999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-412.0258890593668</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>2.970269999999999</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
-        <v>-268.9767626404405</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-268.9767626404405</v>
-      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1910,23 +1868,17 @@
         <v>5.029999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-412.5584190865208</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
         <v>-6.950520000000012</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="n">
-        <v>-276.1867141816644</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-276.1867141816644</v>
-      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1984,23 +1936,17 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-418.9487794123688</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="n">
-        <v>-277.5531491046931</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-277.5531491046931</v>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2058,23 +2004,17 @@
         <v>13.53</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-430.6644400097569</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
         <v>-6.950520000000012</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="n">
-        <v>-288.6749507535681</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-288.6749507535681</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2132,23 +2072,17 @@
         <v>16.53</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-437.054800335605</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
         <v>-3.643590000000017</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
-        <v>-290.8016801727723</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-290.8016801727723</v>
-      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2206,11 +2140,9 @@
         <v>32.53</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0004268805572283324</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-457.7878823655462</v>
-      </c>
+        <v>0.0004970969537898672</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>-2.541280000000015</v>
       </c>
@@ -2278,10 +2210,10 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P25" t="n">
-        <v>100.6997796495444</v>
+        <v>101.4371562026245</v>
       </c>
       <c r="Q25" t="n">
         <v>4.072579999999988</v>
@@ -2290,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>85.40379139366365</v>
+        <v>69.69241441563078</v>
       </c>
       <c r="T25" t="n">
-        <v>85.40379139366365</v>
+        <v>69.69241441563078</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2284,10 @@
         <v>0.25</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P26" t="n">
-        <v>100.0769019423668</v>
+        <v>100.8137765334561</v>
       </c>
       <c r="Q26" t="n">
         <v>-0.3366600000000091</v>
@@ -2364,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>81.93299697387747</v>
+        <v>66.2142037013399</v>
       </c>
       <c r="T26" t="n">
-        <v>81.93299697387747</v>
+        <v>66.2142037013399</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2358,10 @@
         <v>0.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P27" t="n">
-        <v>99.45402423518914</v>
+        <v>100.1903968642878</v>
       </c>
       <c r="Q27" t="n">
         <v>-2.541280000000015</v>
@@ -2438,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>79.98279154644229</v>
+        <v>64.25967914038935</v>
       </c>
       <c r="T27" t="n">
-        <v>79.98279154644229</v>
+        <v>64.25967914038935</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2432,10 @@
         <v>0.53</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P28" t="n">
-        <v>99.37927891032783</v>
+        <v>100.1155913039876</v>
       </c>
       <c r="Q28" t="n">
         <v>-6.950520000000012</v>
@@ -2512,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>76.89005958953014</v>
+        <v>61.16060622479549</v>
       </c>
       <c r="T28" t="n">
-        <v>76.89005958953014</v>
+        <v>61.16060622479549</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2506,10 @@
         <v>0.78</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P29" t="n">
-        <v>98.75640120315019</v>
+        <v>99.4922116348193</v>
       </c>
       <c r="Q29" t="n">
         <v>0.7656499999999937</v>
@@ -2586,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>81.78250462767463</v>
+        <v>66.0626693538764</v>
       </c>
       <c r="T29" t="n">
-        <v>81.78250462767463</v>
+        <v>66.0626693538764</v>
       </c>
     </row>
     <row r="30">
@@ -2648,10 +2580,10 @@
         <v>1.03</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P30" t="n">
-        <v>98.13352349597254</v>
+        <v>98.86883196565097</v>
       </c>
       <c r="Q30" t="n">
         <v>-0.3366600000000091</v>
@@ -2660,10 +2592,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>80.59259369641498</v>
+        <v>64.869987869596</v>
       </c>
       <c r="T30" t="n">
-        <v>80.59259369641498</v>
+        <v>64.869987869596</v>
       </c>
     </row>
     <row r="31">
@@ -2722,10 +2654,10 @@
         <v>1.28</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P31" t="n">
-        <v>97.5106457887949</v>
+        <v>98.24545229648264</v>
       </c>
       <c r="Q31" t="n">
         <v>-3.643590000000017</v>
@@ -2734,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>77.8820937728043</v>
+        <v>62.15362023197528</v>
       </c>
       <c r="T31" t="n">
-        <v>77.8820937728043</v>
+        <v>62.15362023197528</v>
       </c>
     </row>
     <row r="32">
@@ -2796,10 +2728,10 @@
         <v>1.78</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P32" t="n">
-        <v>96.26489037443962</v>
+        <v>96.99869295814598</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2740,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>78.54344989498708</v>
+        <v>62.81562957009517</v>
       </c>
       <c r="T32" t="n">
-        <v>78.54344989498708</v>
+        <v>62.81562957009517</v>
       </c>
     </row>
     <row r="33">
@@ -2870,10 +2802,10 @@
         <v>5.78</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P33" t="n">
-        <v>86.29884705959736</v>
+        <v>87.02461825145274</v>
       </c>
       <c r="Q33" t="n">
         <v>-1.438970000000012</v>
@@ -2882,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>71.66958693364103</v>
+        <v>55.92221504833157</v>
       </c>
       <c r="T33" t="n">
-        <v>71.66958693364103</v>
+        <v>55.92221504833157</v>
       </c>
     </row>
     <row r="34">
@@ -2944,10 +2876,10 @@
         <v>12.78</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0003917723589475649</v>
+        <v>0.0004250523659515542</v>
       </c>
       <c r="P34" t="n">
-        <v>68.8582712586234</v>
+        <v>69.56998751473955</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2956,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>58.88003225510992</v>
+        <v>43.09689655857512</v>
       </c>
       <c r="T34" t="n">
-        <v>58.88003225510992</v>
+        <v>43.09689655857512</v>
       </c>
     </row>
     <row r="35">
@@ -3023,7 +2955,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P35" t="n">
-        <v>97.48138161222877</v>
+        <v>97.48202200435169</v>
       </c>
       <c r="Q35" t="n">
         <v>-0.3366600000000091</v>
@@ -3032,10 +2964,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>82.69035795442029</v>
+        <v>63.91151741421315</v>
       </c>
       <c r="T35" t="n">
-        <v>82.69035795442029</v>
+        <v>63.91151741421315</v>
       </c>
     </row>
     <row r="36">
@@ -3097,7 +3029,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P36" t="n">
-        <v>86.49732811701674</v>
+        <v>86.50076135039353</v>
       </c>
       <c r="Q36" t="n">
         <v>-4.745900000000006</v>
@@ -3106,10 +3038,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>72.07316649065415</v>
+        <v>53.27463090342615</v>
       </c>
       <c r="T36" t="n">
-        <v>72.07316649065415</v>
+        <v>53.27463090342615</v>
       </c>
     </row>
     <row r="37">
@@ -3171,7 +3103,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P37" t="n">
-        <v>85.58199032574908</v>
+        <v>85.58565629589701</v>
       </c>
       <c r="Q37" t="n">
         <v>-2.541280000000015</v>
@@ -3180,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>72.96242102641649</v>
+        <v>54.1658575397576</v>
       </c>
       <c r="T37" t="n">
-        <v>72.96242102641649</v>
+        <v>54.1658575397576</v>
       </c>
     </row>
     <row r="38">
@@ -3245,7 +3177,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P38" t="n">
-        <v>85.21585520924201</v>
+        <v>85.2196142740984</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>74.23047623613205</v>
+        <v>55.43655988629438</v>
       </c>
       <c r="T38" t="n">
-        <v>74.23047623613205</v>
+        <v>55.43655988629438</v>
       </c>
     </row>
     <row r="39">
@@ -3319,7 +3251,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P39" t="n">
-        <v>79.72382846163599</v>
+        <v>79.72898394711933</v>
       </c>
       <c r="Q39" t="n">
         <v>-9.155140000000017</v>
@@ -3328,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>64.36011352719588</v>
+        <v>45.5470581708799</v>
       </c>
       <c r="T39" t="n">
-        <v>64.36011352719588</v>
+        <v>45.5470581708799</v>
       </c>
     </row>
     <row r="40">
@@ -3393,7 +3325,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P40" t="n">
-        <v>70.5704505489593</v>
+        <v>70.57793340215419</v>
       </c>
       <c r="Q40" t="n">
         <v>-2.541280000000015</v>
@@ -3402,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>62.60853593836223</v>
+        <v>43.79352146081224</v>
       </c>
       <c r="T40" t="n">
-        <v>62.60853593836223</v>
+        <v>43.79352146081224</v>
       </c>
     </row>
     <row r="41">
@@ -3467,7 +3399,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P41" t="n">
-        <v>59.58639705374727</v>
+        <v>59.59667274819602</v>
       </c>
       <c r="Q41" t="n">
         <v>-0.3366600000000091</v>
@@ -3476,10 +3408,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>56.55311145164917</v>
+        <v>37.7276934100462</v>
       </c>
       <c r="T41" t="n">
-        <v>56.55311145164917</v>
+        <v>37.7276934100462</v>
       </c>
     </row>
     <row r="42">
@@ -3541,7 +3473,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P42" t="n">
-        <v>55.92504588867659</v>
+        <v>55.93625253020996</v>
       </c>
       <c r="Q42" t="n">
         <v>-9.155140000000017</v>
@@ -3550,10 +3482,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>47.94541765589035</v>
+        <v>29.10311072864944</v>
       </c>
       <c r="T42" t="n">
-        <v>47.94541765589035</v>
+        <v>29.10311072864944</v>
       </c>
     </row>
     <row r="43">
@@ -3615,7 +3547,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P43" t="n">
-        <v>52.26369472360592</v>
+        <v>52.27583231222391</v>
       </c>
       <c r="Q43" t="n">
         <v>-9.155140000000017</v>
@@ -3624,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>45.42007982953565</v>
+        <v>26.57327266061399</v>
       </c>
       <c r="T43" t="n">
-        <v>45.42007982953565</v>
+        <v>26.57327266061399</v>
       </c>
     </row>
     <row r="44">
@@ -3689,7 +3621,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P44" t="n">
-        <v>39.44896564585854</v>
+        <v>39.46436154927272</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3698,10 +3630,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>41.1431644143473</v>
+        <v>22.28989788251087</v>
       </c>
       <c r="T44" t="n">
-        <v>41.1431644143473</v>
+        <v>22.28989788251087</v>
       </c>
     </row>
     <row r="45">
@@ -3765,7 +3697,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P45" t="n">
-        <v>92.74784257442559</v>
+        <v>92.74968653161739</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>77.90491272573492</v>
+        <v>59.11715693479101</v>
       </c>
       <c r="T45" t="n">
-        <v>77.90491272573492</v>
+        <v>59.11715693479101</v>
       </c>
     </row>
     <row r="46">
@@ -3839,7 +3771,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P46" t="n">
-        <v>92.56543444489394</v>
+        <v>92.56732478177148</v>
       </c>
       <c r="Q46" t="n">
         <v>1.867959999999982</v>
@@ -3848,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>80.82027864582669</v>
+        <v>62.03849297529466</v>
       </c>
       <c r="T46" t="n">
-        <v>80.82027864582669</v>
+        <v>62.03849297529466</v>
       </c>
     </row>
     <row r="47">
@@ -3913,7 +3845,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P47" t="n">
-        <v>90.74135314957749</v>
+        <v>90.74370728331236</v>
       </c>
       <c r="Q47" t="n">
         <v>-4.745900000000006</v>
@@ -3922,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>75.0003910226706</v>
+        <v>56.20707185350374</v>
       </c>
       <c r="T47" t="n">
-        <v>75.0003910226706</v>
+        <v>56.20707185350374</v>
       </c>
     </row>
     <row r="48">
@@ -3987,7 +3919,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P48" t="n">
-        <v>72.50054019641297</v>
+        <v>72.50753229872127</v>
       </c>
       <c r="Q48" t="n">
         <v>-6.950520000000012</v>
@@ -3996,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>60.8985955692895</v>
+        <v>42.07975908246393</v>
       </c>
       <c r="T48" t="n">
-        <v>60.8985955692895</v>
+        <v>42.07975908246393</v>
       </c>
     </row>
     <row r="49">
@@ -4061,7 +3993,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P49" t="n">
-        <v>72.13572393734968</v>
+        <v>72.14280879902945</v>
       </c>
       <c r="Q49" t="n">
         <v>1.867959999999982</v>
@@ -4070,10 +4002,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>66.72932740947302</v>
+        <v>47.92243116347123</v>
       </c>
       <c r="T49" t="n">
-        <v>66.72932740947302</v>
+        <v>47.92243116347123</v>
       </c>
     </row>
     <row r="50">
@@ -4135,7 +4067,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P50" t="n">
-        <v>63.01531746076742</v>
+        <v>63.02472130673391</v>
       </c>
       <c r="Q50" t="n">
         <v>1.867959999999982</v>
@@ -4144,10 +4076,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>60.438724178958</v>
+        <v>41.62061785462149</v>
       </c>
       <c r="T50" t="n">
-        <v>60.438724178958</v>
+        <v>41.62061785462149</v>
       </c>
     </row>
     <row r="51">
@@ -4209,7 +4141,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P51" t="n">
-        <v>62.1032768131092</v>
+        <v>62.11291255750434</v>
       </c>
       <c r="Q51" t="n">
         <v>-4.745900000000006</v>
@@ -4218,10 +4150,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>55.24789687885341</v>
+        <v>36.41937806371554</v>
       </c>
       <c r="T51" t="n">
-        <v>55.24789687885341</v>
+        <v>36.41937806371554</v>
       </c>
     </row>
     <row r="52">
@@ -4283,7 +4215,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P52" t="n">
-        <v>52.98287033652694</v>
+        <v>52.9948250652088</v>
       </c>
       <c r="Q52" t="n">
         <v>-0.3366600000000091</v>
@@ -4292,10 +4224,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>51.99847163304045</v>
+        <v>33.16493706154645</v>
       </c>
       <c r="T52" t="n">
-        <v>51.99847163304045</v>
+        <v>33.16493706154645</v>
       </c>
     </row>
     <row r="53">
@@ -4357,7 +4289,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P53" t="n">
-        <v>40.21430126931177</v>
+        <v>40.22950257599503</v>
       </c>
       <c r="Q53" t="n">
         <v>1.867959999999982</v>
@@ -4366,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>44.71221610267042</v>
+        <v>25.86608458249712</v>
       </c>
       <c r="T53" t="n">
-        <v>44.71221610267042</v>
+        <v>25.86608458249712</v>
       </c>
     </row>
     <row r="54">
@@ -4431,7 +4363,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P54" t="n">
-        <v>36.56613867867887</v>
+        <v>36.58226757907681</v>
       </c>
       <c r="Q54" t="n">
         <v>1.867959999999982</v>
@@ -4440,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>42.19597481046442</v>
+        <v>23.34535925895722</v>
       </c>
       <c r="T54" t="n">
-        <v>42.19597481046442</v>
+        <v>23.34535925895722</v>
       </c>
     </row>
     <row r="55">
@@ -4505,7 +4437,7 @@
         <v>-0.0001119825013587284</v>
       </c>
       <c r="P55" t="n">
-        <v>25.62165090678015</v>
+        <v>25.64056258832215</v>
       </c>
       <c r="Q55" t="n">
         <v>-2.541280000000015</v>
@@ -4514,10 +4446,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>31.60607294914432</v>
+        <v>12.73581098165688</v>
       </c>
       <c r="T55" t="n">
-        <v>31.60607294914432</v>
+        <v>12.73581098165688</v>
       </c>
     </row>
     <row r="56">
@@ -4581,7 +4513,7 @@
         <v>-0.0003604901603800431</v>
       </c>
       <c r="P56" t="n">
-        <v>105.5793974757903</v>
+        <v>105.583893776479</v>
       </c>
       <c r="Q56" t="n">
         <v>-1.438970000000012</v>
@@ -4590,10 +4522,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>87.36551949605338</v>
+        <v>68.74914718788874</v>
       </c>
       <c r="T56" t="n">
-        <v>87.36551949605338</v>
+        <v>68.74914718788874</v>
       </c>
     </row>
     <row r="57">
@@ -4655,7 +4587,7 @@
         <v>-0.0003604901603800431</v>
       </c>
       <c r="P57" t="n">
-        <v>88.74068866768972</v>
+        <v>88.73161506260639</v>
       </c>
       <c r="Q57" t="n">
         <v>6.277199999999993</v>
@@ -4664,10 +4596,10 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>81.07344553596373</v>
+        <v>62.43487881386528</v>
       </c>
       <c r="T57" t="n">
-        <v>81.07344553596373</v>
+        <v>62.43487881386528</v>
       </c>
     </row>
     <row r="58">
@@ -4729,7 +4661,7 @@
         <v>-0.0003604901603800431</v>
       </c>
       <c r="P58" t="n">
-        <v>87.33746293368134</v>
+        <v>87.32725850311701</v>
       </c>
       <c r="Q58" t="n">
         <v>6.277199999999993</v>
@@ -4738,10 +4670,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>80.10560091652054</v>
+        <v>61.46428132130573</v>
       </c>
       <c r="T58" t="n">
-        <v>80.10560091652054</v>
+        <v>61.46428132130573</v>
       </c>
     </row>
     <row r="59">
@@ -4803,7 +4735,7 @@
         <v>-0.0003604901603800431</v>
       </c>
       <c r="P59" t="n">
-        <v>83.1277857316562</v>
+        <v>83.11418882464886</v>
       </c>
       <c r="Q59" t="n">
         <v>6.277199999999993</v>
@@ -4812,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>77.20206705819099</v>
+        <v>58.5524888436271</v>
       </c>
       <c r="T59" t="n">
-        <v>77.20206705819099</v>
+        <v>58.5524888436271</v>
       </c>
     </row>
     <row r="60">
@@ -4877,7 +4809,7 @@
         <v>-0.0003604901603800431</v>
       </c>
       <c r="P60" t="n">
-        <v>80.32133426363944</v>
+        <v>80.30547570567009</v>
       </c>
       <c r="Q60" t="n">
         <v>-1.438970000000012</v>
@@ -4886,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>69.94431634607601</v>
+        <v>51.27839232181685</v>
       </c>
       <c r="T60" t="n">
-        <v>69.94431634607601</v>
+        <v>51.27839232181685</v>
       </c>
     </row>
     <row r="61">
@@ -4951,7 +4883,7 @@
         <v>-0.0003604901603800431</v>
       </c>
       <c r="P61" t="n">
-        <v>69.0955283915724</v>
+        <v>69.07062322975501</v>
       </c>
       <c r="Q61" t="n">
         <v>6.277199999999993</v>
@@ -4960,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>67.52362086375912</v>
+        <v>48.8465139180316</v>
       </c>
       <c r="T61" t="n">
-        <v>67.52362086375912</v>
+        <v>48.8465139180316</v>
       </c>
     </row>
     <row r="62">
@@ -5027,7 +4959,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P62" t="n">
-        <v>101.0818798334643</v>
+        <v>101.0827516941018</v>
       </c>
       <c r="Q62" t="n">
         <v>-0.3366600000000091</v>
@@ -5036,10 +4968,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>85.14444921184521</v>
+        <v>66.40010137434854</v>
       </c>
       <c r="T62" t="n">
-        <v>85.14444921184521</v>
+        <v>66.40010137434854</v>
       </c>
     </row>
     <row r="63">
@@ -5101,7 +5033,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P63" t="n">
-        <v>100.3849023771639</v>
+        <v>100.3852125606257</v>
       </c>
       <c r="Q63" t="n">
         <v>-0.3366600000000091</v>
@@ -5110,10 +5042,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>84.66372407646263</v>
+        <v>65.91800889623866</v>
       </c>
       <c r="T63" t="n">
-        <v>84.66372407646263</v>
+        <v>65.91800889623866</v>
       </c>
     </row>
     <row r="64">
@@ -5175,7 +5107,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P64" t="n">
-        <v>92.02117290155995</v>
+        <v>92.01474295891225</v>
       </c>
       <c r="Q64" t="n">
         <v>1.867959999999982</v>
@@ -5184,10 +5116,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>80.4156114442229</v>
+        <v>61.6565853122606</v>
       </c>
       <c r="T64" t="n">
-        <v>80.4156114442229</v>
+        <v>61.6565853122606</v>
       </c>
     </row>
     <row r="65">
@@ -5249,7 +5181,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P65" t="n">
-        <v>80.86953360075462</v>
+        <v>80.85411682329433</v>
       </c>
       <c r="Q65" t="n">
         <v>-0.3366600000000091</v>
@@ -5258,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>71.20342028575085</v>
+        <v>52.41941950916243</v>
       </c>
       <c r="T65" t="n">
-        <v>71.20342028575085</v>
+        <v>52.41941950916243</v>
       </c>
     </row>
     <row r="66">
@@ -5323,7 +5255,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P66" t="n">
-        <v>78.77860123185363</v>
+        <v>78.76149942286597</v>
       </c>
       <c r="Q66" t="n">
         <v>-0.3366600000000091</v>
@@ -5332,10 +5264,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>69.76124487960317</v>
+        <v>50.97314207483283</v>
       </c>
       <c r="T66" t="n">
-        <v>69.76124487960317</v>
+        <v>50.97314207483283</v>
       </c>
     </row>
     <row r="67">
@@ -5397,7 +5329,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P67" t="n">
-        <v>71.80882666885029</v>
+        <v>71.78610808810477</v>
       </c>
       <c r="Q67" t="n">
         <v>1.867959999999982</v>
@@ -5406,10 +5338,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>66.47458251812854</v>
+        <v>47.67590344707449</v>
       </c>
       <c r="T67" t="n">
-        <v>66.47458251812854</v>
+        <v>47.67590344707449</v>
       </c>
     </row>
     <row r="68">
@@ -5471,7 +5403,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P68" t="n">
-        <v>70.41487175624962</v>
+        <v>70.39102982115253</v>
       </c>
       <c r="Q68" t="n">
         <v>1.867959999999982</v>
@@ -5480,10 +5412,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>65.51313224736342</v>
+        <v>46.71171849085476</v>
       </c>
       <c r="T68" t="n">
-        <v>65.51313224736342</v>
+        <v>46.71171849085476</v>
       </c>
     </row>
     <row r="69">
@@ -5545,7 +5477,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P69" t="n">
-        <v>59.2632324554443</v>
+        <v>59.23040368553461</v>
       </c>
       <c r="Q69" t="n">
         <v>-0.3366600000000091</v>
@@ -5554,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>56.30094108889137</v>
+        <v>37.47455268775659</v>
       </c>
       <c r="T69" t="n">
-        <v>56.30094108889137</v>
+        <v>37.47455268775659</v>
       </c>
     </row>
     <row r="70">
@@ -5619,7 +5551,7 @@
         <v>-0.000160490160380043</v>
       </c>
       <c r="P70" t="n">
-        <v>57.1723000865433</v>
+        <v>57.13778628510625</v>
       </c>
       <c r="Q70" t="n">
         <v>-0.3366600000000091</v>
@@ -5628,10 +5560,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>54.85876568274367</v>
+        <v>36.02827525342699</v>
       </c>
       <c r="T70" t="n">
-        <v>54.85876568274367</v>
+        <v>36.02827525342699</v>
       </c>
     </row>
     <row r="71">
@@ -5695,7 +5627,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P71" t="n">
-        <v>112.3049780518679</v>
+        <v>112.3018493480295</v>
       </c>
       <c r="Q71" t="n">
         <v>6.277199999999993</v>
@@ -5704,10 +5636,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>94.63366715305725</v>
+        <v>78.72505109375325</v>
       </c>
       <c r="T71" t="n">
-        <v>94.63366715305725</v>
+        <v>78.72505109375325</v>
       </c>
     </row>
     <row r="72">
@@ -5769,7 +5701,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P72" t="n">
-        <v>109.7172100044359</v>
+        <v>109.7147392749384</v>
       </c>
       <c r="Q72" t="n">
         <v>-2.541280000000015</v>
@@ -5778,10 +5710,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>86.76645410729404</v>
+        <v>70.84226872534292</v>
       </c>
       <c r="T72" t="n">
-        <v>86.76645410729404</v>
+        <v>70.84226872534292</v>
       </c>
     </row>
     <row r="73">
@@ -5843,7 +5775,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P73" t="n">
-        <v>109.3721742647783</v>
+        <v>109.3697912651929</v>
       </c>
       <c r="Q73" t="n">
         <v>6.277199999999993</v>
@@ -5852,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>92.61082913318361</v>
+        <v>76.69860830469767</v>
       </c>
       <c r="T73" t="n">
-        <v>92.61082913318361</v>
+        <v>76.69860830469767</v>
       </c>
     </row>
     <row r="74">
@@ -5917,7 +5849,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P74" t="n">
-        <v>104.1966381699144</v>
+        <v>104.1955711190107</v>
       </c>
       <c r="Q74" t="n">
         <v>6.277199999999993</v>
@@ -5926,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>89.04111498046547</v>
+        <v>73.12253279459961</v>
       </c>
       <c r="T74" t="n">
-        <v>89.04111498046547</v>
+        <v>73.12253279459961</v>
       </c>
     </row>
     <row r="75">
@@ -5991,7 +5923,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P75" t="n">
-        <v>103.3340488207704</v>
+        <v>103.333201094647</v>
       </c>
       <c r="Q75" t="n">
         <v>1.867959999999982</v>
@@ -6000,10 +5932,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>85.40498463697702</v>
+        <v>69.4791479029026</v>
       </c>
       <c r="T75" t="n">
-        <v>85.40498463697702</v>
+        <v>69.4791479029026</v>
       </c>
     </row>
     <row r="76">
@@ -6065,7 +5997,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P76" t="n">
-        <v>102.9890130811128</v>
+        <v>102.9882530849015</v>
       </c>
       <c r="Q76" t="n">
         <v>6.277199999999993</v>
@@ -6074,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>88.20818167816455</v>
+        <v>72.28811517557672</v>
       </c>
       <c r="T76" t="n">
-        <v>88.20818167816455</v>
+        <v>72.28811517557672</v>
       </c>
     </row>
     <row r="77">
@@ -6139,7 +6071,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P77" t="n">
-        <v>92.63794089138499</v>
+        <v>92.63981279253704</v>
       </c>
       <c r="Q77" t="n">
         <v>6.277199999999993</v>
@@ -6148,10 +6080,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>81.06875337272822</v>
+        <v>65.13596415538056</v>
       </c>
       <c r="T77" t="n">
-        <v>81.06875337272822</v>
+        <v>65.13596415538056</v>
       </c>
     </row>
     <row r="78">
@@ -6213,7 +6145,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P78" t="n">
-        <v>89.18758349480903</v>
+        <v>89.19033269508222</v>
       </c>
       <c r="Q78" t="n">
         <v>6.277199999999993</v>
@@ -6222,10 +6154,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>78.68894393758276</v>
+        <v>62.75191381531518</v>
       </c>
       <c r="T78" t="n">
-        <v>78.68894393758276</v>
+        <v>62.75191381531518</v>
       </c>
     </row>
     <row r="79">
@@ -6287,7 +6219,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P79" t="n">
-        <v>77.11133260679323</v>
+        <v>77.11715235399035</v>
       </c>
       <c r="Q79" t="n">
         <v>6.277199999999993</v>
@@ -6296,10 +6228,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>70.35961091457372</v>
+        <v>54.40773762508635</v>
       </c>
       <c r="T79" t="n">
-        <v>70.35961091457372</v>
+        <v>54.40773762508635</v>
       </c>
     </row>
     <row r="80">
@@ -6361,7 +6293,7 @@
         <v>-9.728485643839893e-05</v>
       </c>
       <c r="P80" t="n">
-        <v>58.13436692562551</v>
+        <v>58.14501181798882</v>
       </c>
       <c r="Q80" t="n">
         <v>6.277199999999993</v>
@@ -6370,10 +6302,10 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>57.27065902127379</v>
+        <v>41.29546075472674</v>
       </c>
       <c r="T80" t="n">
-        <v>57.27065902127379</v>
+        <v>41.29546075472674</v>
       </c>
     </row>
     <row r="81">
@@ -6437,7 +6369,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P81" t="n">
-        <v>102.340788815937</v>
+        <v>102.3426752006965</v>
       </c>
       <c r="Q81" t="n">
         <v>-0.3366600000000091</v>
@@ -6446,10 +6378,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>85.97880737130937</v>
+        <v>67.27087638376798</v>
       </c>
       <c r="T81" t="n">
-        <v>85.97880737130937</v>
+        <v>67.27087638376798</v>
       </c>
     </row>
     <row r="82">
@@ -6511,7 +6443,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P82" t="n">
-        <v>100.9442388895369</v>
+        <v>100.9449998286863</v>
       </c>
       <c r="Q82" t="n">
         <v>1.867959999999982</v>
@@ -6520,10 +6452,10 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>86.53615623821808</v>
+        <v>67.82858263526732</v>
       </c>
       <c r="T82" t="n">
-        <v>86.53615623821808</v>
+        <v>67.82858263526732</v>
       </c>
     </row>
     <row r="83">
@@ -6585,7 +6517,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P83" t="n">
-        <v>100.2459639263369</v>
+        <v>100.2461621426812</v>
       </c>
       <c r="Q83" t="n">
         <v>1.867959999999982</v>
@@ -6594,10 +6526,10 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>86.05453617549692</v>
+        <v>67.34559268434681</v>
       </c>
       <c r="T83" t="n">
-        <v>86.05453617549692</v>
+        <v>67.34559268434681</v>
       </c>
     </row>
     <row r="84">
@@ -6659,7 +6591,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P84" t="n">
-        <v>91.86666436793624</v>
+        <v>91.86010991062022</v>
       </c>
       <c r="Q84" t="n">
         <v>-0.3366600000000091</v>
@@ -6668,10 +6600,10 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>78.75450643049199</v>
+        <v>60.02602711996057</v>
       </c>
       <c r="T84" t="n">
-        <v>78.75450643049199</v>
+        <v>60.02602711996057</v>
       </c>
     </row>
     <row r="85">
@@ -6733,7 +6665,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P85" t="n">
-        <v>90.47011444153613</v>
+        <v>90.46243453861004</v>
       </c>
       <c r="Q85" t="n">
         <v>-2.541280000000015</v>
@@ -6742,10 +6674,10 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>76.27067731269862</v>
+        <v>57.53636106477924</v>
       </c>
       <c r="T85" t="n">
-        <v>76.27067731269862</v>
+        <v>57.53636106477924</v>
       </c>
     </row>
     <row r="86">
@@ -6807,7 +6739,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P86" t="n">
-        <v>69.5218655455345</v>
+        <v>69.49730395845747</v>
       </c>
       <c r="Q86" t="n">
         <v>-0.3366600000000091</v>
@@ -6816,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>63.34266442341487</v>
+        <v>44.5703486905047</v>
       </c>
       <c r="T86" t="n">
-        <v>63.34266442341487</v>
+        <v>44.5703486905047</v>
       </c>
     </row>
     <row r="87">
@@ -6881,7 +6813,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P87" t="n">
-        <v>65.33221576633417</v>
+        <v>65.30427784242696</v>
       </c>
       <c r="Q87" t="n">
         <v>-6.950520000000012</v>
@@ -6890,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>55.89117707003481</v>
+        <v>37.10135052496076</v>
       </c>
       <c r="T87" t="n">
-        <v>55.89117707003481</v>
+        <v>37.10135052496076</v>
       </c>
     </row>
     <row r="88">
@@ -6955,7 +6887,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P88" t="n">
-        <v>63.93566583993406</v>
+        <v>63.90660247041678</v>
       </c>
       <c r="Q88" t="n">
         <v>1.867959999999982</v>
@@ -6964,10 +6896,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>61.01029291399661</v>
+        <v>42.23011523648105</v>
       </c>
       <c r="T88" t="n">
-        <v>61.01029291399661</v>
+        <v>42.23011523648105</v>
       </c>
     </row>
     <row r="89">
@@ -7029,7 +6961,7 @@
         <v>-0.0002167401603800451</v>
       </c>
       <c r="P89" t="n">
-        <v>63.23739087673401</v>
+        <v>63.20776478441169</v>
       </c>
       <c r="Q89" t="n">
         <v>1.867959999999982</v>
@@ -7038,10 +6970,10 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>60.52867285127545</v>
+        <v>41.74712528556056</v>
       </c>
       <c r="T89" t="n">
-        <v>60.52867285127545</v>
+        <v>41.74712528556056</v>
       </c>
     </row>
     <row r="90">
@@ -7102,10 +7034,10 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P90" t="n">
-        <v>94.79218959815701</v>
+        <v>94.75894740352882</v>
       </c>
       <c r="Q90" t="n">
         <v>4.072579999999988</v>
@@ -7114,10 +7046,10 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>84.03957944714276</v>
+        <v>65.07688236189927</v>
       </c>
       <c r="T90" t="n">
-        <v>84.03957944714276</v>
+        <v>65.07688236189927</v>
       </c>
     </row>
     <row r="91">
@@ -7176,10 +7108,10 @@
         <v>0.1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P91" t="n">
-        <v>94.4943867567431</v>
+        <v>94.4597900101206</v>
       </c>
       <c r="Q91" t="n">
         <v>0.7656499999999937</v>
@@ -7188,10 +7120,10 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>81.55329288573068</v>
+        <v>62.58459551470057</v>
       </c>
       <c r="T91" t="n">
-        <v>81.55329288573068</v>
+        <v>62.58459551470057</v>
       </c>
     </row>
     <row r="92">
@@ -7250,10 +7182,10 @@
         <v>0.85</v>
       </c>
       <c r="O92" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P92" t="n">
-        <v>92.26086544613881</v>
+        <v>92.21610955955894</v>
       </c>
       <c r="Q92" t="n">
         <v>4.072579999999988</v>
@@ -7262,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>82.29365332761594</v>
+        <v>63.3194426157994</v>
       </c>
       <c r="T92" t="n">
-        <v>82.29365332761594</v>
+        <v>63.3194426157994</v>
       </c>
     </row>
     <row r="93">
@@ -7324,10 +7256,10 @@
         <v>0.95</v>
       </c>
       <c r="O93" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P93" t="n">
-        <v>91.9630626047249</v>
+        <v>91.91695216615074</v>
       </c>
       <c r="Q93" t="n">
         <v>-5.848210000000009</v>
@@ -7336,10 +7268,10 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>75.24559978915079</v>
+        <v>56.25609730857974</v>
       </c>
       <c r="T93" t="n">
-        <v>75.24559978915079</v>
+        <v>56.25609730857974</v>
       </c>
     </row>
     <row r="94">
@@ -7398,10 +7330,10 @@
         <v>1.05</v>
       </c>
       <c r="O94" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P94" t="n">
-        <v>91.66525976331098</v>
+        <v>91.61779477274251</v>
       </c>
       <c r="Q94" t="n">
         <v>-2.541280000000015</v>
@@ -7410,10 +7342,10 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>77.32108020479183</v>
+        <v>58.33486892140201</v>
       </c>
       <c r="T94" t="n">
-        <v>77.32108020479183</v>
+        <v>58.33486892140201</v>
       </c>
     </row>
     <row r="95">
@@ -7472,10 +7404,10 @@
         <v>1.8</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P95" t="n">
-        <v>89.43173845270668</v>
+        <v>89.37411432218086</v>
       </c>
       <c r="Q95" t="n">
         <v>-2.541280000000015</v>
@@ -7484,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>75.78055715815051</v>
+        <v>56.78418679249037</v>
       </c>
       <c r="T95" t="n">
-        <v>75.78055715815051</v>
+        <v>56.78418679249037</v>
       </c>
     </row>
     <row r="96">
@@ -7546,10 +7478,10 @@
         <v>3.8</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P96" t="n">
-        <v>83.47568162442856</v>
+        <v>83.39096645401645</v>
       </c>
       <c r="Q96" t="n">
         <v>-2.541280000000015</v>
@@ -7558,10 +7490,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>71.67249570044038</v>
+        <v>52.64903444872601</v>
       </c>
       <c r="T96" t="n">
-        <v>71.67249570044038</v>
+        <v>52.64903444872601</v>
       </c>
     </row>
     <row r="97">
@@ -7620,10 +7552,10 @@
         <v>4.55</v>
       </c>
       <c r="O97" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P97" t="n">
-        <v>81.24216031382426</v>
+        <v>81.14728600345479</v>
       </c>
       <c r="Q97" t="n">
         <v>-3.643590000000017</v>
@@ -7632,10 +7564,10 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>69.37167815762356</v>
+        <v>50.3365092431442</v>
       </c>
       <c r="T97" t="n">
-        <v>69.37167815762356</v>
+        <v>50.3365092431442</v>
       </c>
     </row>
     <row r="98">
@@ -7694,10 +7626,10 @@
         <v>4.649999999999999</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P98" t="n">
-        <v>80.94435747241035</v>
+        <v>80.84812861004659</v>
       </c>
       <c r="Q98" t="n">
         <v>1.867959999999982</v>
@@ -7706,10 +7638,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>72.96774756561564</v>
+        <v>53.9389670093068</v>
       </c>
       <c r="T98" t="n">
-        <v>72.96774756561564</v>
+        <v>53.9389670093068</v>
       </c>
     </row>
     <row r="99">
@@ -7768,10 +7700,10 @@
         <v>5.399999999999999</v>
       </c>
       <c r="O99" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P99" t="n">
-        <v>78.71083616180604</v>
+        <v>78.60444815948493</v>
       </c>
       <c r="Q99" t="n">
         <v>1.867959999999982</v>
@@ -7780,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>71.42722451897433</v>
+        <v>52.38828488039517</v>
       </c>
       <c r="T99" t="n">
-        <v>71.42722451897433</v>
+        <v>52.38828488039517</v>
       </c>
     </row>
     <row r="100">
@@ -7844,22 +7776,22 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P100" t="n">
-        <v>100.6752327033736</v>
+        <v>100.6735032085733</v>
       </c>
       <c r="Q100" t="n">
         <v>8.481819999999999</v>
       </c>
       <c r="R100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>94.56894553893945</v>
+        <v>72.21200075784013</v>
       </c>
       <c r="T100" t="n">
-        <v>94.56894553893945</v>
+        <v>72.21200075784013</v>
       </c>
     </row>
     <row r="101">
@@ -7918,22 +7850,22 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P101" t="n">
-        <v>97.68254896542044</v>
+        <v>97.66720729114472</v>
       </c>
       <c r="Q101" t="n">
         <v>-9.155140000000017</v>
       </c>
       <c r="R101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>80.34009467844872</v>
+        <v>57.94476050725427</v>
       </c>
       <c r="T101" t="n">
-        <v>80.34009467844872</v>
+        <v>57.94476050725427</v>
       </c>
     </row>
     <row r="102">
@@ -7992,22 +7924,22 @@
         <v>3</v>
       </c>
       <c r="O102" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P102" t="n">
-        <v>91.69718148951405</v>
+        <v>91.65461545628764</v>
       </c>
       <c r="Q102" t="n">
         <v>-13.56438000000001</v>
       </c>
       <c r="R102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>73.17063885038176</v>
+        <v>50.74188615284711</v>
       </c>
       <c r="T102" t="n">
-        <v>73.17063885038176</v>
+        <v>50.74188615284711</v>
       </c>
     </row>
     <row r="103">
@@ -8066,22 +7998,22 @@
         <v>3.15</v>
       </c>
       <c r="O103" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P103" t="n">
-        <v>91.24827892882108</v>
+        <v>91.20367106867336</v>
       </c>
       <c r="Q103" t="n">
         <v>5.174889999999976</v>
       </c>
       <c r="R103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>85.78602444711315</v>
+        <v>63.38155580266037</v>
       </c>
       <c r="T103" t="n">
-        <v>85.78602444711315</v>
+        <v>63.38155580266037</v>
       </c>
     </row>
     <row r="104">
@@ -8140,22 +8072,22 @@
         <v>3.3</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P104" t="n">
-        <v>90.79937636812809</v>
+        <v>90.75272668105907</v>
       </c>
       <c r="Q104" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>80.15434213563218</v>
+        <v>57.73699161238975</v>
       </c>
       <c r="T104" t="n">
-        <v>80.15434213563218</v>
+        <v>57.73699161238975</v>
       </c>
     </row>
     <row r="105">
@@ -8214,22 +8146,22 @@
         <v>3.4</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P105" t="n">
-        <v>90.50010799433278</v>
+        <v>90.45209708931623</v>
       </c>
       <c r="Q105" t="n">
         <v>6.277199999999993</v>
       </c>
       <c r="R105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>86.03028421286807</v>
+        <v>63.62396112336474</v>
       </c>
       <c r="T105" t="n">
-        <v>86.03028421286807</v>
+        <v>63.62396112336474</v>
       </c>
     </row>
     <row r="106">
@@ -8288,22 +8220,22 @@
         <v>4.4</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P106" t="n">
-        <v>87.50742425637958</v>
+        <v>87.44580117188768</v>
       </c>
       <c r="Q106" t="n">
         <v>10.68643999999998</v>
       </c>
       <c r="R106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>87.00732327588766</v>
+        <v>64.59358240618211</v>
       </c>
       <c r="T106" t="n">
-        <v>87.00732327588766</v>
+        <v>64.59358240618211</v>
       </c>
     </row>
     <row r="107">
@@ -8362,22 +8294,22 @@
         <v>5.4</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P107" t="n">
-        <v>84.51474051842638</v>
+        <v>84.43950525445914</v>
       </c>
       <c r="Q107" t="n">
         <v>-6.950520000000012</v>
       </c>
       <c r="R107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>72.77847241539696</v>
+        <v>50.32634215559626</v>
       </c>
       <c r="T107" t="n">
-        <v>72.77847241539696</v>
+        <v>50.32634215559626</v>
       </c>
     </row>
     <row r="108">
@@ -8436,22 +8368,22 @@
         <v>6.4</v>
       </c>
       <c r="O108" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P108" t="n">
-        <v>81.52205678047319</v>
+        <v>81.4332093370306</v>
       </c>
       <c r="Q108" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>76.79668946311864</v>
+        <v>54.3433357450943</v>
       </c>
       <c r="T108" t="n">
-        <v>76.79668946311864</v>
+        <v>54.3433357450943</v>
       </c>
     </row>
     <row r="109">
@@ -8510,16 +8442,16 @@
         <v>36.4</v>
       </c>
       <c r="O109" t="n">
-        <v>0.0001277838204883533</v>
+        <v>0.0001289903739936572</v>
       </c>
       <c r="P109" t="n">
-        <v>16.28308095933974</v>
+        <v>15.89750947002729</v>
       </c>
       <c r="Q109" t="n">
         <v>0.7656499999999937</v>
       </c>
       <c r="R109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -8582,10 +8514,10 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P110" t="n">
-        <v>102.6281195789724</v>
+        <v>102.6352587612312</v>
       </c>
       <c r="Q110" t="n">
         <v>8.481819999999999</v>
@@ -8594,10 +8526,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>92.41496144444037</v>
+        <v>73.56783521993493</v>
       </c>
       <c r="T110" t="n">
-        <v>92.41496144444037</v>
+        <v>73.56783521993493</v>
       </c>
     </row>
     <row r="111">
@@ -8656,10 +8588,10 @@
         <v>0.25</v>
       </c>
       <c r="O111" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P111" t="n">
-        <v>101.8777666540975</v>
+        <v>101.8814928667352</v>
       </c>
       <c r="Q111" t="n">
         <v>2.970269999999999</v>
@@ -8668,10 +8600,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>88.09594925243653</v>
+        <v>69.23766717521673</v>
       </c>
       <c r="T111" t="n">
-        <v>88.09594925243653</v>
+        <v>69.23766717521673</v>
       </c>
     </row>
     <row r="112">
@@ -8730,10 +8662,10 @@
         <v>2.25</v>
       </c>
       <c r="O112" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P112" t="n">
-        <v>95.87494325509813</v>
+        <v>95.85136571076693</v>
       </c>
       <c r="Q112" t="n">
         <v>-13.56438000000001</v>
@@ -8742,10 +8674,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>72.55121412079362</v>
+        <v>53.64239973422511</v>
       </c>
       <c r="T112" t="n">
-        <v>72.55121412079362</v>
+        <v>53.64239973422511</v>
       </c>
     </row>
     <row r="113">
@@ -8804,10 +8736,10 @@
         <v>3.75</v>
       </c>
       <c r="O113" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P113" t="n">
-        <v>91.37282570584863</v>
+        <v>91.32877034379072</v>
       </c>
       <c r="Q113" t="n">
         <v>2.970269999999999</v>
@@ -8816,10 +8748,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>80.85039329666873</v>
+        <v>61.94432991607317</v>
       </c>
       <c r="T113" t="n">
-        <v>80.85039329666873</v>
+        <v>61.94432991607317</v>
       </c>
     </row>
     <row r="114">
@@ -8878,10 +8810,10 @@
         <v>3.9</v>
       </c>
       <c r="O114" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P114" t="n">
-        <v>90.92261395092368</v>
+        <v>90.8765108070931</v>
       </c>
       <c r="Q114" t="n">
         <v>0.7656499999999937</v>
@@ -8890,10 +8822,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>79.01928047764193</v>
+        <v>60.1080721659124</v>
       </c>
       <c r="T114" t="n">
-        <v>79.01928047764193</v>
+        <v>60.1080721659124</v>
       </c>
     </row>
     <row r="115">
@@ -8952,10 +8884,10 @@
         <v>4</v>
       </c>
       <c r="O115" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P115" t="n">
-        <v>90.62247278097371</v>
+        <v>90.5750044492947</v>
       </c>
       <c r="Q115" t="n">
         <v>-8.052830000000014</v>
@@ -8964,10 +8896,10 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>72.7299086237873</v>
+        <v>53.80494648800415</v>
       </c>
       <c r="T115" t="n">
-        <v>72.7299086237873</v>
+        <v>53.80494648800415</v>
       </c>
     </row>
     <row r="116">
@@ -9026,10 +8958,10 @@
         <v>4.1</v>
       </c>
       <c r="O116" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P116" t="n">
-        <v>90.32233161102376</v>
+        <v>90.27349809149628</v>
       </c>
       <c r="Q116" t="n">
         <v>-2.541280000000015</v>
@@ -9038,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>76.32436522021437</v>
+        <v>57.405780806808</v>
       </c>
       <c r="T116" t="n">
-        <v>76.32436522021437</v>
+        <v>57.405780806808</v>
       </c>
     </row>
     <row r="117">
@@ -9100,10 +9032,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O117" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P117" t="n">
-        <v>90.02219044107379</v>
+        <v>89.97199173369786</v>
       </c>
       <c r="Q117" t="n">
         <v>2.970269999999999</v>
@@ -9112,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>79.91882181664144</v>
+        <v>61.00661512561186</v>
       </c>
       <c r="T117" t="n">
-        <v>79.91882181664144</v>
+        <v>61.00661512561186</v>
       </c>
     </row>
     <row r="118">
@@ -9174,10 +9106,10 @@
         <v>4.35</v>
       </c>
       <c r="O118" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P118" t="n">
-        <v>89.57197868614884</v>
+        <v>89.51973219700024</v>
       </c>
       <c r="Q118" t="n">
         <v>-4.745900000000006</v>
@@ -9186,10 +9118,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>74.28623651673708</v>
+        <v>55.36114199210028</v>
       </c>
       <c r="T118" t="n">
-        <v>74.28623651673708</v>
+        <v>55.36114199210028</v>
       </c>
     </row>
     <row r="119">
@@ -9248,10 +9180,10 @@
         <v>4.5</v>
       </c>
       <c r="O119" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P119" t="n">
-        <v>89.12176693122389</v>
+        <v>89.06747266030263</v>
       </c>
       <c r="Q119" t="n">
         <v>-5.848210000000009</v>
@@ -9260,10 +9192,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>73.2154181938858</v>
+        <v>54.28672731860968</v>
       </c>
       <c r="T119" t="n">
-        <v>73.2154181938858</v>
+        <v>54.28672731860968</v>
       </c>
     </row>
     <row r="120">
@@ -9322,10 +9254,10 @@
         <v>5.5</v>
       </c>
       <c r="O120" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P120" t="n">
-        <v>86.12035523172422</v>
+        <v>86.05240908231849</v>
       </c>
       <c r="Q120" t="n">
         <v>5.174889999999976</v>
@@ -9334,10 +9266,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>78.74820431113585</v>
+        <v>59.8213474398417</v>
       </c>
       <c r="T120" t="n">
-        <v>78.74820431113585</v>
+        <v>59.8213474398417</v>
       </c>
     </row>
     <row r="121">
@@ -9396,10 +9328,10 @@
         <v>7</v>
       </c>
       <c r="O121" t="n">
-        <v>4.111715382168963e-05</v>
+        <v>4.232370732699362e-05</v>
       </c>
       <c r="P121" t="n">
-        <v>81.61823768247473</v>
+        <v>81.52981371534227</v>
       </c>
       <c r="Q121" t="n">
         <v>8.481819999999999</v>
@@ -9408,10 +9340,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>77.9238495329048</v>
+        <v>58.98116070164782</v>
       </c>
       <c r="T121" t="n">
-        <v>77.9238495329048</v>
+        <v>58.98116070164782</v>
       </c>
     </row>
     <row r="122">
@@ -9472,10 +9404,10 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P122" t="n">
-        <v>116.3884936205004</v>
+        <v>116.4581230141041</v>
       </c>
       <c r="Q122" t="n">
         <v>0.7656499999999937</v>
@@ -9484,10 +9416,10 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>96.22372981719612</v>
+        <v>77.78837457627994</v>
       </c>
       <c r="T122" t="n">
-        <v>96.22372981719612</v>
+        <v>77.78837457627994</v>
       </c>
     </row>
     <row r="123">
@@ -9546,10 +9478,10 @@
         <v>0.25</v>
       </c>
       <c r="O123" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P123" t="n">
-        <v>115.6227660191658</v>
+        <v>115.6889125116508</v>
       </c>
       <c r="Q123" t="n">
         <v>0.7656499999999937</v>
@@ -9558,10 +9490,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>95.69558575530387</v>
+        <v>77.25674763304615</v>
       </c>
       <c r="T123" t="n">
-        <v>95.69558575530387</v>
+        <v>77.25674763304615</v>
       </c>
     </row>
     <row r="124">
@@ -9620,10 +9552,10 @@
         <v>0.35</v>
       </c>
       <c r="O124" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P124" t="n">
-        <v>115.3164749786319</v>
+        <v>115.3812283106695</v>
       </c>
       <c r="Q124" t="n">
         <v>8.481819999999999</v>
@@ -9632,10 +9564,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>100.8063896037756</v>
+        <v>82.37699839244377</v>
       </c>
       <c r="T124" t="n">
-        <v>100.8063896037756</v>
+        <v>82.37699839244377</v>
       </c>
     </row>
     <row r="125">
@@ -9694,10 +9626,10 @@
         <v>1.1</v>
       </c>
       <c r="O125" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P125" t="n">
-        <v>113.0192921746278</v>
+        <v>113.0735968033095</v>
       </c>
       <c r="Q125" t="n">
         <v>0.7656499999999937</v>
@@ -9706,10 +9638,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>93.89989594487021</v>
+        <v>75.44921602605127</v>
       </c>
       <c r="T125" t="n">
-        <v>93.89989594487021</v>
+        <v>75.44921602605127</v>
       </c>
     </row>
     <row r="126">
@@ -9768,10 +9700,10 @@
         <v>3.1</v>
       </c>
       <c r="O126" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P126" t="n">
-        <v>106.8934713639503</v>
+        <v>106.919912783683</v>
       </c>
       <c r="Q126" t="n">
         <v>4.072579999999988</v>
@@ -9780,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>91.95562693825876</v>
+        <v>73.48172971019147</v>
       </c>
       <c r="T126" t="n">
-        <v>91.95562693825876</v>
+        <v>73.48172971019147</v>
       </c>
     </row>
     <row r="127">
@@ -9842,10 +9774,10 @@
         <v>4.1</v>
       </c>
       <c r="O127" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P127" t="n">
-        <v>103.8305609586115</v>
+        <v>103.8430707738698</v>
       </c>
       <c r="Q127" t="n">
         <v>-2.541280000000015</v>
@@ -9854,10 +9786,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>85.28128371363665</v>
+        <v>66.78416347723537</v>
       </c>
       <c r="T127" t="n">
-        <v>85.28128371363665</v>
+        <v>66.78416347723537</v>
       </c>
     </row>
     <row r="128">
@@ -9916,10 +9848,10 @@
         <v>5.6</v>
       </c>
       <c r="O128" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P128" t="n">
-        <v>99.23619535060332</v>
+        <v>99.22780775914987</v>
       </c>
       <c r="Q128" t="n">
         <v>0.7656499999999937</v>
@@ -9928,10 +9860,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>84.3933028308097</v>
+        <v>65.87993104784314</v>
       </c>
       <c r="T128" t="n">
-        <v>84.3933028308097</v>
+        <v>65.87993104784314</v>
       </c>
     </row>
     <row r="129">
@@ -9990,10 +9922,10 @@
         <v>20.6</v>
       </c>
       <c r="O129" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P129" t="n">
-        <v>54.20460599858907</v>
+        <v>53.99140771207447</v>
       </c>
       <c r="Q129" t="n">
         <v>-5.848210000000009</v>
@@ -10060,10 +9992,10 @@
         <v>26.6</v>
       </c>
       <c r="O130" t="n">
-        <v>-0.0005555495128449792</v>
+        <v>-0.0005543429593396752</v>
       </c>
       <c r="P130" t="n">
-        <v>45.01587478257275</v>
+        <v>44.7608816826347</v>
       </c>
       <c r="Q130" t="n">
         <v>-2.541280000000015</v>
@@ -10132,22 +10064,22 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P131" t="n">
-        <v>79.9692114618471</v>
+        <v>79.70785339941607</v>
       </c>
       <c r="Q131" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R131" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>71.45380436541406</v>
+        <v>50.86535568377194</v>
       </c>
       <c r="T131" t="n">
-        <v>71.45380436541406</v>
+        <v>50.86535568377194</v>
       </c>
     </row>
     <row r="132">
@@ -10206,22 +10138,22 @@
         <v>0.75</v>
       </c>
       <c r="O132" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P132" t="n">
-        <v>78.37325997257373</v>
+        <v>78.10667147076987</v>
       </c>
       <c r="Q132" t="n">
         <v>2.970269999999999</v>
       </c>
       <c r="R132" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>73.39420930672756</v>
+        <v>52.8060979437067</v>
       </c>
       <c r="T132" t="n">
-        <v>73.39420930672756</v>
+        <v>52.8060979437067</v>
       </c>
     </row>
     <row r="133">
@@ -10280,22 +10212,22 @@
         <v>2.75</v>
       </c>
       <c r="O133" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P133" t="n">
-        <v>74.11738933451144</v>
+        <v>73.83685299437998</v>
       </c>
       <c r="Q133" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R133" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>69.69852002818251</v>
+        <v>49.09324140904741</v>
       </c>
       <c r="T133" t="n">
-        <v>69.69852002818251</v>
+        <v>49.09324140904741</v>
       </c>
     </row>
     <row r="134">
@@ -10354,22 +10286,22 @@
         <v>4.25</v>
       </c>
       <c r="O134" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P134" t="n">
-        <v>70.92548635596472</v>
+        <v>70.63448913708757</v>
       </c>
       <c r="Q134" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R134" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>64.45579595670331</v>
+        <v>43.83260900887493</v>
       </c>
       <c r="T134" t="n">
-        <v>64.45579595670331</v>
+        <v>43.83260900887493</v>
       </c>
     </row>
     <row r="135">
@@ -10428,22 +10360,22 @@
         <v>4.4</v>
       </c>
       <c r="O135" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P135" t="n">
-        <v>70.60629605811005</v>
+        <v>70.31425275135834</v>
       </c>
       <c r="Q135" t="n">
         <v>6.277199999999993</v>
       </c>
       <c r="R135" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>70.31799731742973</v>
+        <v>49.70602761288706</v>
       </c>
       <c r="T135" t="n">
-        <v>70.31799731742973</v>
+        <v>49.70602761288706</v>
       </c>
     </row>
     <row r="136">
@@ -10502,22 +10434,22 @@
         <v>4.430000000000001</v>
       </c>
       <c r="O136" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P136" t="n">
-        <v>70.54245799853911</v>
+        <v>70.25020547421248</v>
       </c>
       <c r="Q136" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R136" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>61.91072693776351</v>
+        <v>41.28148856764543</v>
       </c>
       <c r="T136" t="n">
-        <v>61.91072693776351</v>
+        <v>41.28148856764543</v>
       </c>
     </row>
     <row r="137">
@@ -10576,22 +10508,22 @@
         <v>6.430000000000001</v>
       </c>
       <c r="O137" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P137" t="n">
-        <v>66.28658736047682</v>
+        <v>65.98038699782261</v>
       </c>
       <c r="Q137" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R137" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>62.01651014009606</v>
+        <v>41.37784741633698</v>
       </c>
       <c r="T137" t="n">
-        <v>62.01651014009606</v>
+        <v>41.37784741633698</v>
       </c>
     </row>
     <row r="138">
@@ -10650,16 +10582,16 @@
         <v>36.43</v>
       </c>
       <c r="O138" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P138" t="n">
-        <v>19.93086016295134</v>
+        <v>19.47274586039458</v>
       </c>
       <c r="Q138" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R138" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -10722,10 +10654,10 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P139" t="n">
-        <v>101.0668938564867</v>
+        <v>100.9709481963064</v>
       </c>
       <c r="Q139" t="n">
         <v>1.867959999999982</v>
@@ -10734,10 +10666,10 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>86.81705673104638</v>
+        <v>67.84651641453291</v>
       </c>
       <c r="T139" t="n">
-        <v>86.81705673104638</v>
+        <v>67.84651641453291</v>
       </c>
     </row>
     <row r="140">
@@ -10796,10 +10728,10 @@
         <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P140" t="n">
-        <v>98.9044523749578</v>
+        <v>98.80141970797158</v>
       </c>
       <c r="Q140" t="n">
         <v>-1.438970000000012</v>
@@ -10808,10 +10740,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>83.04467597159966</v>
+        <v>64.06155394117293</v>
       </c>
       <c r="T140" t="n">
-        <v>83.04467597159966</v>
+        <v>64.06155394117293</v>
       </c>
     </row>
     <row r="141">
@@ -10870,10 +10802,10 @@
         <v>3</v>
       </c>
       <c r="O141" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P141" t="n">
-        <v>94.57956941190002</v>
+        <v>94.46236273130189</v>
       </c>
       <c r="Q141" t="n">
         <v>6.277199999999993</v>
@@ -10882,10 +10814,10 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>85.38374290298786</v>
+        <v>66.39558899116508</v>
       </c>
       <c r="T141" t="n">
-        <v>85.38374290298786</v>
+        <v>66.39558899116508</v>
       </c>
     </row>
     <row r="142">
@@ -10944,10 +10876,10 @@
         <v>3.5</v>
       </c>
       <c r="O142" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P142" t="n">
-        <v>93.49834867113559</v>
+        <v>93.37759848713448</v>
       </c>
       <c r="Q142" t="n">
         <v>1.867959999999982</v>
@@ -10956,10 +10888,10 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>81.59681628282571</v>
+        <v>62.59850006280968</v>
       </c>
       <c r="T142" t="n">
-        <v>81.59681628282571</v>
+        <v>62.59850006280968</v>
       </c>
     </row>
     <row r="143">
@@ -11018,10 +10950,10 @@
         <v>3.6</v>
       </c>
       <c r="O143" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P143" t="n">
-        <v>93.28210452298269</v>
+        <v>93.16064563830099</v>
       </c>
       <c r="Q143" t="n">
         <v>1.867959999999982</v>
@@ -11030,10 +10962,10 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>81.44766655573368</v>
+        <v>62.44855673847474</v>
       </c>
       <c r="T143" t="n">
-        <v>81.44766655573368</v>
+        <v>62.44855673847474</v>
       </c>
     </row>
     <row r="144">
@@ -11092,10 +11024,10 @@
         <v>3.85</v>
       </c>
       <c r="O144" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P144" t="n">
-        <v>92.74149415260048</v>
+        <v>92.61826351621727</v>
       </c>
       <c r="Q144" t="n">
         <v>6.277199999999993</v>
@@ -11104,10 +11036,10 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>84.11597022270571</v>
+        <v>65.121070734318</v>
       </c>
       <c r="T144" t="n">
-        <v>84.11597022270571</v>
+        <v>65.121070734318</v>
       </c>
     </row>
     <row r="145">
@@ -11166,10 +11098,10 @@
         <v>10.85</v>
       </c>
       <c r="O145" t="n">
-        <v>0.0001085300624353845</v>
+        <v>0.0001141072810003276</v>
       </c>
       <c r="P145" t="n">
-        <v>77.60440378189828</v>
+        <v>77.43156409787338</v>
       </c>
       <c r="Q145" t="n">
         <v>1.867959999999982</v>
@@ -11178,10 +11110,10 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>70.63431134156228</v>
+        <v>51.57766572419088</v>
       </c>
       <c r="T145" t="n">
-        <v>70.63431134156228</v>
+        <v>51.57766572419088</v>
       </c>
     </row>
     <row r="146">
@@ -11242,10 +11174,10 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P146" t="n">
-        <v>73.92888944574398</v>
+        <v>74.00456228072609</v>
       </c>
       <c r="Q146" t="n">
         <v>5.174889999999976</v>
@@ -11254,10 +11186,10 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>70.40986362141477</v>
+        <v>51.49468010073027</v>
       </c>
       <c r="T146" t="n">
-        <v>70.40986362141477</v>
+        <v>51.49468010073027</v>
       </c>
     </row>
     <row r="147">
@@ -11316,10 +11248,10 @@
         <v>1.5</v>
       </c>
       <c r="O147" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P147" t="n">
-        <v>71.38253122644457</v>
+        <v>71.4759686831087</v>
       </c>
       <c r="Q147" t="n">
         <v>5.174889999999976</v>
@@ -11328,10 +11260,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>68.65356807894068</v>
+        <v>49.74708502669728</v>
       </c>
       <c r="T147" t="n">
-        <v>68.65356807894068</v>
+        <v>49.74708502669728</v>
       </c>
     </row>
     <row r="148">
@@ -11390,10 +11322,10 @@
         <v>2.5</v>
       </c>
       <c r="O148" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P148" t="n">
-        <v>69.68495908024498</v>
+        <v>69.79023961803044</v>
       </c>
       <c r="Q148" t="n">
         <v>5.174889999999976</v>
@@ -11402,10 +11334,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>67.48270438395795</v>
+        <v>48.58202164400862</v>
       </c>
       <c r="T148" t="n">
-        <v>67.48270438395795</v>
+        <v>48.58202164400862</v>
       </c>
     </row>
     <row r="149">
@@ -11464,10 +11396,10 @@
         <v>2.6</v>
       </c>
       <c r="O149" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P149" t="n">
-        <v>69.51520186562502</v>
+        <v>69.62166671152261</v>
       </c>
       <c r="Q149" t="n">
         <v>-4.745900000000006</v>
@@ -11476,10 +11408,10 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>60.52296754888005</v>
+        <v>41.6089276157083</v>
       </c>
       <c r="T149" t="n">
-        <v>60.52296754888005</v>
+        <v>41.6089276157083</v>
       </c>
     </row>
     <row r="150">
@@ -11538,10 +11470,10 @@
         <v>4.6</v>
       </c>
       <c r="O150" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P150" t="n">
-        <v>66.12005757322581</v>
+        <v>66.2502085813661</v>
       </c>
       <c r="Q150" t="n">
         <v>-4.745900000000006</v>
@@ -11550,10 +11482,10 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>58.18124015891458</v>
+        <v>39.27880085033098</v>
       </c>
       <c r="T150" t="n">
-        <v>58.18124015891458</v>
+        <v>39.27880085033098</v>
       </c>
     </row>
     <row r="151">
@@ -11612,10 +11544,10 @@
         <v>4.85</v>
       </c>
       <c r="O151" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P151" t="n">
-        <v>65.69566453667591</v>
+        <v>65.82877631509653</v>
       </c>
       <c r="Q151" t="n">
         <v>0.7656499999999937</v>
@@ -11624,10 +11556,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>61.68999671604647</v>
+        <v>42.79675038800963</v>
       </c>
       <c r="T151" t="n">
-        <v>61.68999671604647</v>
+        <v>42.79675038800963</v>
       </c>
     </row>
     <row r="152">
@@ -11686,10 +11618,10 @@
         <v>5.6</v>
       </c>
       <c r="O152" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P152" t="n">
-        <v>64.42248542702622</v>
+        <v>64.56447951628783</v>
       </c>
       <c r="Q152" t="n">
         <v>-0.3366600000000091</v>
@@ -11698,10 +11630,10 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>60.05155444863392</v>
+        <v>41.16110977432297</v>
       </c>
       <c r="T152" t="n">
-        <v>60.05155444863392</v>
+        <v>41.16110977432297</v>
       </c>
     </row>
     <row r="153">
@@ -11760,10 +11692,10 @@
         <v>6.35</v>
       </c>
       <c r="O153" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P153" t="n">
-        <v>63.14930631737651</v>
+        <v>63.30018271747914</v>
       </c>
       <c r="Q153" t="n">
         <v>2.970269999999999</v>
@@ -11772,10 +11704,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>61.45429016592342</v>
+        <v>42.57284146731697</v>
       </c>
       <c r="T153" t="n">
-        <v>61.45429016592342</v>
+        <v>42.57284146731697</v>
       </c>
     </row>
     <row r="154">
@@ -11834,10 +11766,10 @@
         <v>6.449999999999999</v>
       </c>
       <c r="O154" t="n">
-        <v>0.0001578675296269827</v>
+        <v>0.0001588611619254684</v>
       </c>
       <c r="P154" t="n">
-        <v>62.97954910275655</v>
+        <v>63.13160981097131</v>
       </c>
       <c r="Q154" t="n">
         <v>1.867959999999982</v>
@@ -11846,10 +11778,10 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>60.57690930024962</v>
+        <v>41.69449205237792</v>
       </c>
       <c r="T154" t="n">
-        <v>60.57690930024962</v>
+        <v>41.69449205237792</v>
       </c>
     </row>
     <row r="155">
@@ -11913,7 +11845,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P155" t="n">
-        <v>103.3747974146705</v>
+        <v>103.3858576965097</v>
       </c>
       <c r="Q155" t="n">
         <v>-0.3366600000000091</v>
@@ -11922,10 +11854,10 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>81.00611687309872</v>
+        <v>67.99185447717072</v>
       </c>
       <c r="T155" t="n">
-        <v>81.00611687309872</v>
+        <v>67.99185447717072</v>
       </c>
     </row>
     <row r="156">
@@ -11987,7 +11919,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P156" t="n">
-        <v>100.2077497469338</v>
+        <v>100.2084306087666</v>
       </c>
       <c r="Q156" t="n">
         <v>-0.3366600000000091</v>
@@ -11996,10 +11928,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>78.8217141997077</v>
+        <v>65.79582901389698</v>
       </c>
       <c r="T156" t="n">
-        <v>78.8217141997077</v>
+        <v>65.79582901389698</v>
       </c>
     </row>
     <row r="157">
@@ -12061,7 +11993,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P157" t="n">
-        <v>100.1021814913426</v>
+        <v>100.1025163725085</v>
       </c>
       <c r="Q157" t="n">
         <v>-0.3366600000000091</v>
@@ -12070,10 +12002,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>78.74890077726131</v>
+        <v>65.72262816512121</v>
       </c>
       <c r="T157" t="n">
-        <v>78.74890077726131</v>
+        <v>65.72262816512121</v>
       </c>
     </row>
     <row r="158">
@@ -12135,7 +12067,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P158" t="n">
-        <v>97.46297510156208</v>
+        <v>97.45466046605601</v>
       </c>
       <c r="Q158" t="n">
         <v>-0.3366600000000091</v>
@@ -12144,10 +12076,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>76.92856521610214</v>
+        <v>63.89260694572643</v>
       </c>
       <c r="T158" t="n">
-        <v>76.92856521610214</v>
+        <v>63.89260694572643</v>
       </c>
     </row>
     <row r="159">
@@ -12209,7 +12141,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P159" t="n">
-        <v>97.35740684597086</v>
+        <v>97.34874622979791</v>
       </c>
       <c r="Q159" t="n">
         <v>-0.3366600000000091</v>
@@ -12218,10 +12150,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>76.85575179365576</v>
+        <v>63.81940609695063</v>
       </c>
       <c r="T159" t="n">
-        <v>76.85575179365576</v>
+        <v>63.81940609695063</v>
       </c>
     </row>
     <row r="160">
@@ -12283,7 +12215,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P160" t="n">
-        <v>95.77388301210254</v>
+        <v>95.76003268592639</v>
       </c>
       <c r="Q160" t="n">
         <v>-0.3366600000000091</v>
@@ -12292,10 +12224,10 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>75.76355045696026</v>
+        <v>62.72139336531376</v>
       </c>
       <c r="T160" t="n">
-        <v>75.76355045696026</v>
+        <v>62.72139336531376</v>
       </c>
     </row>
     <row r="161">
@@ -12357,7 +12289,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P161" t="n">
-        <v>95.24604173414643</v>
+        <v>95.23046150463588</v>
       </c>
       <c r="Q161" t="n">
         <v>-0.3366600000000091</v>
@@ -12366,10 +12298,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>75.39948334472841</v>
+        <v>62.35538912143481</v>
       </c>
       <c r="T161" t="n">
-        <v>75.39948334472841</v>
+        <v>62.35538912143481</v>
       </c>
     </row>
     <row r="162">
@@ -12431,7 +12363,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P162" t="n">
-        <v>93.66251790027812</v>
+        <v>93.64174796076438</v>
       </c>
       <c r="Q162" t="n">
         <v>-0.3366600000000091</v>
@@ -12440,10 +12372,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>74.30728200803289</v>
+        <v>61.25737638979795</v>
       </c>
       <c r="T162" t="n">
-        <v>74.30728200803289</v>
+        <v>61.25737638979795</v>
       </c>
     </row>
     <row r="163">
@@ -12505,7 +12437,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P163" t="n">
-        <v>92.6068353443659</v>
+        <v>92.58260559818336</v>
       </c>
       <c r="Q163" t="n">
         <v>-0.3366600000000091</v>
@@ -12514,10 +12446,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>73.57914778356921</v>
+        <v>60.52536790204004</v>
       </c>
       <c r="T163" t="n">
-        <v>73.57914778356921</v>
+        <v>60.52536790204004</v>
       </c>
     </row>
     <row r="164">
@@ -12579,7 +12511,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P164" t="n">
-        <v>92.07899406640981</v>
+        <v>92.05303441689286</v>
       </c>
       <c r="Q164" t="n">
         <v>-0.3366600000000091</v>
@@ -12588,10 +12520,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>73.21508067133739</v>
+        <v>60.15936365816108</v>
       </c>
       <c r="T164" t="n">
-        <v>73.21508067133739</v>
+        <v>60.15936365816108</v>
       </c>
     </row>
     <row r="165">
@@ -12653,7 +12585,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P165" t="n">
-        <v>91.02331151049759</v>
+        <v>90.99389205431184</v>
       </c>
       <c r="Q165" t="n">
         <v>-0.3366600000000091</v>
@@ -12662,10 +12594,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>72.48694644687372</v>
+        <v>59.42735517040317</v>
       </c>
       <c r="T165" t="n">
-        <v>72.48694644687372</v>
+        <v>59.42735517040317</v>
       </c>
     </row>
     <row r="166">
@@ -12727,7 +12659,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P166" t="n">
-        <v>87.85626384276095</v>
+        <v>87.81646496656882</v>
       </c>
       <c r="Q166" t="n">
         <v>-0.3366600000000091</v>
@@ -12736,10 +12668,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>70.30254377348267</v>
+        <v>57.23132970712945</v>
       </c>
       <c r="T166" t="n">
-        <v>70.30254377348267</v>
+        <v>57.23132970712945</v>
       </c>
     </row>
     <row r="167">
@@ -12801,7 +12733,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P167" t="n">
-        <v>58.66608042035898</v>
+        <v>58.5306160520142</v>
       </c>
       <c r="Q167" t="n">
         <v>-0.3366600000000091</v>
@@ -12871,7 +12803,7 @@
         <v>-6.63967859189163e-05</v>
       </c>
       <c r="P168" t="n">
-        <v>37.55242930211473</v>
+        <v>37.34776880039398</v>
       </c>
       <c r="Q168" t="n">
         <v>-0.3366600000000091</v>
@@ -13829,7 +13761,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P182" t="n">
-        <v>99.49988798126853</v>
+        <v>99.4987087023504</v>
       </c>
       <c r="Q182" t="n">
         <v>-4.745900000000006</v>
@@ -13838,10 +13770,10 @@
         <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>75.38876769661265</v>
+        <v>62.25794430982872</v>
       </c>
       <c r="T182" t="n">
-        <v>75.38876769661265</v>
+        <v>62.25794430982872</v>
       </c>
     </row>
     <row r="183">
@@ -13903,7 +13835,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P183" t="n">
-        <v>93.53463240677465</v>
+        <v>93.51938687894261</v>
       </c>
       <c r="Q183" t="n">
         <v>8.481819999999999</v>
@@ -13912,10 +13844,10 @@
         <v>0</v>
       </c>
       <c r="S183" t="n">
-        <v>80.39789555663641</v>
+        <v>67.26755319279758</v>
       </c>
       <c r="T183" t="n">
-        <v>80.39789555663641</v>
+        <v>67.26755319279758</v>
       </c>
     </row>
     <row r="184">
@@ -13977,7 +13909,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P184" t="n">
-        <v>89.80634767271597</v>
+        <v>89.78231073931275</v>
       </c>
       <c r="Q184" t="n">
         <v>-3.643590000000017</v>
@@ -13986,10 +13918,10 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>69.46315228990422</v>
+        <v>56.3044618262551</v>
       </c>
       <c r="T184" t="n">
-        <v>69.46315228990422</v>
+        <v>56.3044618262551</v>
       </c>
     </row>
     <row r="185">
@@ -14051,7 +13983,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P185" t="n">
-        <v>87.56937683228077</v>
+        <v>87.54006505553482</v>
       </c>
       <c r="Q185" t="n">
         <v>-3.643590000000017</v>
@@ -14060,10 +13992,10 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>67.9202500046233</v>
+        <v>54.75477131235269</v>
       </c>
       <c r="T185" t="n">
-        <v>67.9202500046233</v>
+        <v>54.75477131235269</v>
       </c>
     </row>
     <row r="186">
@@ -14125,7 +14057,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P186" t="n">
-        <v>85.33240599184555</v>
+        <v>85.29781937175692</v>
       </c>
       <c r="Q186" t="n">
         <v>-3.643590000000017</v>
@@ -14134,10 +14066,10 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>66.37734771934237</v>
+        <v>53.2050807984503</v>
       </c>
       <c r="T186" t="n">
-        <v>66.37734771934237</v>
+        <v>53.2050807984503</v>
       </c>
     </row>
     <row r="187">
@@ -14199,7 +14131,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P187" t="n">
-        <v>83.84109209822208</v>
+        <v>83.80298891590496</v>
       </c>
       <c r="Q187" t="n">
         <v>-1.438970000000012</v>
@@ -14208,10 +14140,10 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>66.8693351881728</v>
+        <v>53.69563994252235</v>
       </c>
       <c r="T187" t="n">
-        <v>66.8693351881728</v>
+        <v>53.69563994252235</v>
       </c>
     </row>
     <row r="188">
@@ -14273,7 +14205,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P188" t="n">
-        <v>83.69196070885974</v>
+        <v>83.65350587031978</v>
       </c>
       <c r="Q188" t="n">
         <v>8.481819999999999</v>
@@ -14282,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>73.60912550140038</v>
+        <v>60.44891493162699</v>
       </c>
       <c r="T188" t="n">
-        <v>73.60912550140038</v>
+        <v>60.44891493162699</v>
       </c>
     </row>
     <row r="189">
@@ -14347,7 +14279,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P189" t="n">
-        <v>82.946303762048</v>
+        <v>82.90609064239379</v>
       </c>
       <c r="Q189" t="n">
         <v>-3.643590000000017</v>
@@ -14356,10 +14288,10 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>64.7315852817094</v>
+        <v>51.55207758362106</v>
       </c>
       <c r="T189" t="n">
-        <v>64.7315852817094</v>
+        <v>51.55207758362106</v>
       </c>
     </row>
     <row r="190">
@@ -14421,7 +14353,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P190" t="n">
-        <v>79.96367597480105</v>
+        <v>79.91642973068991</v>
       </c>
       <c r="Q190" t="n">
         <v>-8.052830000000014</v>
@@ -14430,10 +14362,10 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>59.63320424996612</v>
+        <v>46.43845125840387</v>
       </c>
       <c r="T190" t="n">
-        <v>59.63320424996612</v>
+        <v>46.43845125840387</v>
       </c>
     </row>
     <row r="191">
@@ -14495,7 +14427,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P191" t="n">
-        <v>65.05053703856635</v>
+        <v>64.96812517217045</v>
       </c>
       <c r="Q191" t="n">
         <v>-8.052830000000014</v>
@@ -14504,10 +14436,10 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>49.34718901476003</v>
+        <v>36.10718116572117</v>
       </c>
       <c r="T191" t="n">
-        <v>49.34718901476003</v>
+        <v>36.10718116572117</v>
       </c>
     </row>
     <row r="192">
@@ -14569,7 +14501,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P192" t="n">
-        <v>57.59396757044899</v>
+        <v>57.49397289291072</v>
       </c>
       <c r="Q192" t="n">
         <v>-4.745900000000006</v>
@@ -14578,10 +14510,10 @@
         <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>46.48506488568353</v>
+        <v>33.2270753493903</v>
       </c>
       <c r="T192" t="n">
-        <v>46.48506488568353</v>
+        <v>33.2270753493903</v>
       </c>
     </row>
     <row r="193">
@@ -14643,7 +14575,7 @@
         <v>9.344280770562548e-05</v>
       </c>
       <c r="P193" t="n">
-        <v>51.6287119959551</v>
+        <v>51.51465106950293</v>
       </c>
       <c r="Q193" t="n">
         <v>2.970269999999999</v>
@@ -14652,10 +14584,10 @@
         <v>0</v>
       </c>
       <c r="S193" t="n">
-        <v>47.6927202648297</v>
+        <v>34.42746884900836</v>
       </c>
       <c r="T193" t="n">
-        <v>47.6927202648297</v>
+        <v>34.42746884900836</v>
       </c>
     </row>
     <row r="194">
@@ -14719,7 +14651,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P194" t="n">
-        <v>107.7551700093205</v>
+        <v>107.7734569293624</v>
       </c>
       <c r="Q194" t="n">
         <v>-11.35976000000001</v>
@@ -14728,10 +14660,10 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>76.29966172655939</v>
+        <v>63.40583936373559</v>
       </c>
       <c r="T194" t="n">
-        <v>76.29966172655939</v>
+        <v>63.40583936373559</v>
       </c>
     </row>
     <row r="195">
@@ -14793,7 +14725,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P195" t="n">
-        <v>106.9996479056987</v>
+        <v>107.0161532822952</v>
       </c>
       <c r="Q195" t="n">
         <v>-11.35976000000001</v>
@@ -14802,10 +14734,10 @@
         <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>75.77855668612379</v>
+        <v>62.88244164398773</v>
       </c>
       <c r="T195" t="n">
-        <v>75.77855668612379</v>
+        <v>62.88244164398773</v>
       </c>
     </row>
     <row r="196">
@@ -14867,7 +14799,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P196" t="n">
-        <v>101.7109931803463</v>
+        <v>101.7150277528242</v>
       </c>
       <c r="Q196" t="n">
         <v>5.174889999999976</v>
@@ -14876,10 +14808,10 @@
         <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>83.53523884570721</v>
+        <v>70.64630375580508</v>
       </c>
       <c r="T196" t="n">
-        <v>83.53523884570721</v>
+        <v>70.64630375580508</v>
       </c>
     </row>
     <row r="197">
@@ -14941,7 +14873,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P197" t="n">
-        <v>96.42233845499382</v>
+        <v>96.41390222335323</v>
       </c>
       <c r="Q197" t="n">
         <v>8.481819999999999</v>
@@ -14950,10 +14882,10 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>82.16838705118444</v>
+        <v>69.26804894758051</v>
       </c>
       <c r="T197" t="n">
-        <v>82.16838705118444</v>
+        <v>69.26804894758051</v>
       </c>
     </row>
     <row r="198">
@@ -15015,7 +14947,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P198" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q198" t="n">
         <v>8.481819999999999</v>
@@ -15024,10 +14956,10 @@
         <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>80.60507192987758</v>
+        <v>67.69785578833691</v>
       </c>
       <c r="T198" t="n">
-        <v>80.60507192987758</v>
+        <v>67.69785578833691</v>
       </c>
     </row>
     <row r="199">
@@ -15089,7 +15021,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P199" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q199" t="n">
         <v>-5.848210000000009</v>
@@ -15098,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>70.72124347959588</v>
+        <v>57.7938957916248</v>
       </c>
       <c r="T199" t="n">
-        <v>70.72124347959588</v>
+        <v>57.7938957916248</v>
       </c>
     </row>
     <row r="200">
@@ -15163,7 +15095,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P200" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q200" t="n">
         <v>7.379509999999982</v>
@@ -15172,10 +15104,10 @@
         <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>79.84477743370208</v>
+        <v>66.93601271166673</v>
       </c>
       <c r="T200" t="n">
-        <v>79.84477743370208</v>
+        <v>66.93601271166673</v>
       </c>
     </row>
     <row r="201">
@@ -15237,7 +15169,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P201" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q201" t="n">
         <v>0.7656499999999937</v>
@@ -15246,10 +15178,10 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>75.283010456649</v>
+        <v>62.36495425164577</v>
       </c>
       <c r="T201" t="n">
-        <v>75.283010456649</v>
+        <v>62.36495425164577</v>
       </c>
     </row>
     <row r="202">
@@ -15311,7 +15243,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P202" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q202" t="n">
         <v>-11.35976000000001</v>
@@ -15320,10 +15252,10 @@
         <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>66.91977099871831</v>
+        <v>53.98468040827399</v>
       </c>
       <c r="T202" t="n">
-        <v>66.91977099871831</v>
+        <v>53.98468040827399</v>
       </c>
     </row>
     <row r="203">
@@ -15385,7 +15317,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P203" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q203" t="n">
         <v>8.481819999999999</v>
@@ -15394,10 +15326,10 @@
         <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>80.60507192987758</v>
+        <v>67.69785578833691</v>
       </c>
       <c r="T203" t="n">
-        <v>80.60507192987758</v>
+        <v>67.69785578833691</v>
       </c>
     </row>
     <row r="204">
@@ -15459,7 +15391,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P204" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q204" t="n">
         <v>-4.745900000000006</v>
@@ -15468,10 +15400,10 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>71.4815379757714</v>
+        <v>58.55573886829497</v>
       </c>
       <c r="T204" t="n">
-        <v>71.4815379757714</v>
+        <v>58.55573886829497</v>
       </c>
     </row>
     <row r="205">
@@ -15533,7 +15465,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P205" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q205" t="n">
         <v>-6.950520000000012</v>
@@ -15542,10 +15474,10 @@
         <v>0</v>
       </c>
       <c r="S205" t="n">
-        <v>69.96094898342037</v>
+        <v>57.03205271495464</v>
       </c>
       <c r="T205" t="n">
-        <v>69.96094898342037</v>
+        <v>57.03205271495464</v>
       </c>
     </row>
     <row r="206">
@@ -15607,7 +15539,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P206" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q206" t="n">
         <v>-4.745900000000006</v>
@@ -15616,10 +15548,10 @@
         <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>71.4815379757714</v>
+        <v>58.55573886829497</v>
       </c>
       <c r="T206" t="n">
-        <v>71.4815379757714</v>
+        <v>58.55573886829497</v>
       </c>
     </row>
     <row r="207">
@@ -15681,7 +15613,7 @@
         <v>-0.0002731518374384543</v>
       </c>
       <c r="P207" t="n">
-        <v>94.15577214412849</v>
+        <v>94.14199128215139</v>
       </c>
       <c r="Q207" t="n">
         <v>6.277199999999993</v>
@@ -15690,10 +15622,10 @@
         <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>79.08448293752654</v>
+        <v>66.17416963499659</v>
       </c>
       <c r="T207" t="n">
-        <v>79.08448293752654</v>
+        <v>66.17416963499659</v>
       </c>
     </row>
     <row r="208">
@@ -15754,10 +15686,10 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P208" t="n">
-        <v>103.0463310911433</v>
+        <v>103.1453171228686</v>
       </c>
       <c r="Q208" t="n">
         <v>-0.3366600000000091</v>
@@ -15766,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="S208" t="n">
-        <v>86.38041496684691</v>
+        <v>67.82560889227469</v>
       </c>
       <c r="T208" t="n">
-        <v>86.38041496684691</v>
+        <v>67.82560889227469</v>
       </c>
     </row>
     <row r="209">
@@ -15828,10 +15760,10 @@
         <v>5</v>
       </c>
       <c r="O209" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P209" t="n">
-        <v>84.34962732858419</v>
+        <v>84.45336724516642</v>
       </c>
       <c r="Q209" t="n">
         <v>-6.950520000000012</v>
@@ -15840,10 +15772,10 @@
         <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>68.92300069701976</v>
+        <v>50.33592263808232</v>
       </c>
       <c r="T209" t="n">
-        <v>68.92300069701976</v>
+        <v>50.33592263808232</v>
       </c>
     </row>
     <row r="210">
@@ -15902,10 +15834,10 @@
         <v>11</v>
       </c>
       <c r="O210" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P210" t="n">
-        <v>61.91358281351322</v>
+        <v>62.02302739192384</v>
       </c>
       <c r="Q210" t="n">
         <v>-0.3366600000000091</v>
@@ -15914,10 +15846,10 @@
         <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>58.00999092274398</v>
+        <v>39.40462774509763</v>
       </c>
       <c r="T210" t="n">
-        <v>58.00999092274398</v>
+        <v>39.40462774509763</v>
       </c>
     </row>
     <row r="211">
@@ -15976,10 +15908,10 @@
         <v>11.05</v>
       </c>
       <c r="O211" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P211" t="n">
-        <v>61.72661577588762</v>
+        <v>61.83610789314681</v>
       </c>
       <c r="Q211" t="n">
         <v>-4.745900000000006</v>
@@ -15988,10 +15920,10 @@
         <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>54.83985646511417</v>
+        <v>36.22806916047526</v>
       </c>
       <c r="T211" t="n">
-        <v>54.83985646511417</v>
+        <v>36.22806916047526</v>
       </c>
     </row>
     <row r="212">
@@ -16050,10 +15982,10 @@
         <v>13.05</v>
       </c>
       <c r="O212" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P212" t="n">
-        <v>54.24793427086396</v>
+        <v>54.35932794206595</v>
       </c>
       <c r="Q212" t="n">
         <v>-0.3366600000000091</v>
@@ -16062,10 +15994,10 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>52.72277553270661</v>
+        <v>34.10799034948735</v>
       </c>
       <c r="T212" t="n">
-        <v>52.72277553270661</v>
+        <v>34.10799034948735</v>
       </c>
     </row>
     <row r="213">
@@ -16124,10 +16056,10 @@
         <v>15.05</v>
       </c>
       <c r="O213" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P213" t="n">
-        <v>46.7692527658403</v>
+        <v>46.88254799098509</v>
       </c>
       <c r="Q213" t="n">
         <v>-0.3366600000000091</v>
@@ -16136,10 +16068,10 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>47.56451661559699</v>
+        <v>28.9405392318188</v>
       </c>
       <c r="T213" t="n">
-        <v>47.56451661559699</v>
+        <v>28.9405392318188</v>
       </c>
     </row>
     <row r="214">
@@ -16198,10 +16130,10 @@
         <v>15.55</v>
       </c>
       <c r="O214" t="n">
-        <v>-0.0003576256202240432</v>
+        <v>-0.0003709683429540752</v>
       </c>
       <c r="P214" t="n">
-        <v>44.89958238958438</v>
+        <v>45.01335300321487</v>
       </c>
       <c r="Q214" t="n">
         <v>-9.155140000000017</v>
@@ -16210,10 +16142,10 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>40.19259591691545</v>
+        <v>21.55393183904035</v>
       </c>
       <c r="T214" t="n">
-        <v>40.19259591691545</v>
+        <v>21.55393183904035</v>
       </c>
     </row>
     <row r="215">
@@ -16274,10 +16206,10 @@
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>-0.0006753544574410726</v>
+        <v>-0.0007190877459701306</v>
       </c>
       <c r="P215" t="n">
-        <v>110.3225302626883</v>
+        <v>111.1417111406361</v>
       </c>
       <c r="Q215" t="n">
         <v>-6.950520000000012</v>
@@ -16286,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>86.64549846984683</v>
+        <v>68.78112410097022</v>
       </c>
       <c r="T215" t="n">
-        <v>86.64549846984683</v>
+        <v>68.78112410097022</v>
       </c>
     </row>
     <row r="216">
@@ -16348,10 +16280,10 @@
         <v>4</v>
       </c>
       <c r="O216" t="n">
-        <v>-0.0006753544574410726</v>
+        <v>-0.0007190877459701306</v>
       </c>
       <c r="P216" t="n">
-        <v>97.31592808246234</v>
+        <v>98.1044390081329</v>
       </c>
       <c r="Q216" t="n">
         <v>-2.541280000000015</v>
@@ -16360,10 +16292,10 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>80.71565373719146</v>
+        <v>62.81800433843948</v>
       </c>
       <c r="T216" t="n">
-        <v>80.71565373719146</v>
+        <v>62.81800433843948</v>
       </c>
     </row>
     <row r="217">
@@ -16422,10 +16354,10 @@
         <v>6</v>
       </c>
       <c r="O217" t="n">
-        <v>-0.0006753544574410726</v>
+        <v>-0.0007190877459701306</v>
       </c>
       <c r="P217" t="n">
-        <v>90.81262699234935</v>
+        <v>91.5858029418813</v>
       </c>
       <c r="Q217" t="n">
         <v>1.867959999999982</v>
@@ -16434,10 +16366,10 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>79.2713203632148</v>
+        <v>61.36013061051443</v>
       </c>
       <c r="T217" t="n">
-        <v>79.2713203632148</v>
+        <v>61.36013061051443</v>
       </c>
     </row>
     <row r="218">
@@ -16496,10 +16428,10 @@
         <v>6.25</v>
       </c>
       <c r="O218" t="n">
-        <v>-0.0006753544574410726</v>
+        <v>-0.0007190877459701306</v>
       </c>
       <c r="P218" t="n">
-        <v>89.99971435608522</v>
+        <v>90.77097343359985</v>
       </c>
       <c r="Q218" t="n">
         <v>-6.950520000000012</v>
@@ -16508,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>72.62827547397583</v>
+        <v>54.70223024282743</v>
       </c>
       <c r="T218" t="n">
-        <v>72.62827547397583</v>
+        <v>54.70223024282743</v>
       </c>
     </row>
     <row r="219">
@@ -16570,10 +16502,10 @@
         <v>12.25</v>
       </c>
       <c r="O219" t="n">
-        <v>-0.0006753544574410726</v>
+        <v>-0.0007190877459701306</v>
       </c>
       <c r="P219" t="n">
-        <v>70.48981108574625</v>
+        <v>71.21506523484506</v>
       </c>
       <c r="Q219" t="n">
         <v>-11.35976000000001</v>
@@ -16582,10 +16514,10 @@
         <v>0</v>
       </c>
       <c r="S219" t="n">
-        <v>56.13056341323762</v>
+        <v>38.13911983232971</v>
       </c>
       <c r="T219" t="n">
-        <v>56.13056341323762</v>
+        <v>38.13911983232971</v>
       </c>
     </row>
     <row r="220">
@@ -16644,10 +16576,10 @@
         <v>14.75</v>
       </c>
       <c r="O220" t="n">
-        <v>-0.0006753544574410726</v>
+        <v>-0.0007190877459701306</v>
       </c>
       <c r="P220" t="n">
-        <v>62.36068472310502</v>
+        <v>63.06677015203056</v>
       </c>
       <c r="Q220" t="n">
         <v>-11.35976000000001</v>
@@ -16656,10 +16588,10 @@
         <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>50.52367421488923</v>
+        <v>32.5075622890726</v>
       </c>
       <c r="T220" t="n">
-        <v>50.52367421488923</v>
+        <v>32.5075622890726</v>
       </c>
     </row>
     <row r="221">
@@ -16720,10 +16652,10 @@
         <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P221" t="n">
-        <v>92.03996231770086</v>
+        <v>93.57724748127369</v>
       </c>
       <c r="Q221" t="n">
         <v>-6.950520000000012</v>
@@ -16732,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>74.30918586068209</v>
+        <v>56.64173950470428</v>
       </c>
       <c r="T221" t="n">
-        <v>74.30918586068209</v>
+        <v>56.64173950470428</v>
       </c>
     </row>
     <row r="222">
@@ -16794,10 +16726,10 @@
         <v>1.5</v>
       </c>
       <c r="O222" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P222" t="n">
-        <v>87.26565490591349</v>
+        <v>88.7916821115318</v>
       </c>
       <c r="Q222" t="n">
         <v>-0.3366600000000091</v>
@@ -16806,10 +16738,10 @@
         <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>75.57797749664972</v>
+        <v>57.90533468770668</v>
       </c>
       <c r="T222" t="n">
-        <v>75.57797749664972</v>
+        <v>57.90533468770668</v>
       </c>
     </row>
     <row r="223">
@@ -16868,10 +16800,10 @@
         <v>3</v>
       </c>
       <c r="O223" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P223" t="n">
-        <v>82.49134749412613</v>
+        <v>84.00611674178991</v>
       </c>
       <c r="Q223" t="n">
         <v>-0.3366600000000091</v>
@@ -16880,10 +16812,10 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>72.28500215556429</v>
+        <v>54.59787141068811</v>
       </c>
       <c r="T223" t="n">
-        <v>72.28500215556429</v>
+        <v>54.59787141068811</v>
       </c>
     </row>
     <row r="224">
@@ -16942,10 +16874,10 @@
         <v>3.75</v>
       </c>
       <c r="O224" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P224" t="n">
-        <v>80.10419378823246</v>
+        <v>81.61333405691897</v>
       </c>
       <c r="Q224" t="n">
         <v>-4.745900000000006</v>
@@ -16954,10 +16886,10 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>67.59733650031951</v>
+        <v>49.89676746549818</v>
       </c>
       <c r="T224" t="n">
-        <v>67.59733650031951</v>
+        <v>49.89676746549818</v>
       </c>
     </row>
     <row r="225">
@@ -17016,10 +16948,10 @@
         <v>4.25</v>
       </c>
       <c r="O225" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P225" t="n">
-        <v>78.51275798430333</v>
+        <v>80.01814560033833</v>
       </c>
       <c r="Q225" t="n">
         <v>-9.155140000000017</v>
@@ -17028,10 +16960,10 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>63.45850006858895</v>
+        <v>45.74690739981132</v>
       </c>
       <c r="T225" t="n">
-        <v>63.45850006858895</v>
+        <v>45.74690739981132</v>
       </c>
     </row>
     <row r="226">
@@ -17090,10 +17022,10 @@
         <v>9.25</v>
       </c>
       <c r="O226" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P226" t="n">
-        <v>62.59839994501214</v>
+        <v>64.06626103453203</v>
       </c>
       <c r="Q226" t="n">
         <v>-0.3366600000000091</v>
@@ -17102,10 +17034,10 @@
         <v>0</v>
       </c>
       <c r="S226" t="n">
-        <v>58.56427156770825</v>
+        <v>40.81677442311072</v>
       </c>
       <c r="T226" t="n">
-        <v>58.56427156770825</v>
+        <v>40.81677442311072</v>
       </c>
     </row>
     <row r="227">
@@ -17164,10 +17096,10 @@
         <v>10.75</v>
       </c>
       <c r="O227" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P227" t="n">
-        <v>57.82409253322479</v>
+        <v>59.28069566479015</v>
       </c>
       <c r="Q227" t="n">
         <v>-11.35976000000001</v>
@@ -17176,10 +17108,10 @@
         <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>47.66835126486766</v>
+        <v>29.89088037939053</v>
       </c>
       <c r="T227" t="n">
-        <v>47.66835126486766</v>
+        <v>29.89088037939053</v>
       </c>
     </row>
     <row r="228">
@@ -17238,10 +17170,10 @@
         <v>12.75</v>
       </c>
       <c r="O228" t="n">
-        <v>-0.0002218471816896999</v>
+        <v>-0.0002307423301763879</v>
       </c>
       <c r="P228" t="n">
-        <v>51.4583493175083</v>
+        <v>52.89994183846763</v>
       </c>
       <c r="Q228" t="n">
         <v>-15.76900000000001</v>
@@ -17250,10 +17182,10 @@
         <v>0</v>
       </c>
       <c r="S228" t="n">
-        <v>40.23653949205166</v>
+        <v>22.43355703668512</v>
       </c>
       <c r="T228" t="n">
-        <v>40.23653949205166</v>
+        <v>22.43355703668512</v>
       </c>
     </row>
     <row r="229">
@@ -17317,19 +17249,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P229" t="n">
-        <v>88.74385689816107</v>
+        <v>88.70696694601533</v>
       </c>
       <c r="Q229" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R229" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>74.64734159550498</v>
+        <v>59.37047137461951</v>
       </c>
       <c r="T229" t="n">
-        <v>74.64734159550498</v>
+        <v>59.37047137461951</v>
       </c>
     </row>
     <row r="230">
@@ -17391,19 +17323,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P230" t="n">
-        <v>88.65065059398971</v>
+        <v>88.61345517521393</v>
       </c>
       <c r="Q230" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R230" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>74.58305456184807</v>
+        <v>59.30584228192125</v>
       </c>
       <c r="T230" t="n">
-        <v>74.58305456184807</v>
+        <v>59.30584228192125</v>
       </c>
     </row>
     <row r="231">
@@ -17465,19 +17397,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P231" t="n">
-        <v>85.85446146884898</v>
+        <v>85.80810205117201</v>
       </c>
       <c r="Q231" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R231" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>72.6544435521409</v>
+        <v>57.36696950097365</v>
       </c>
       <c r="T231" t="n">
-        <v>72.6544435521409</v>
+        <v>57.36696950097365</v>
       </c>
     </row>
     <row r="232">
@@ -17539,19 +17471,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P232" t="n">
-        <v>85.38842994799219</v>
+        <v>85.34054319716502</v>
       </c>
       <c r="Q232" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R232" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>67.01094691062777</v>
+        <v>51.71092250079126</v>
       </c>
       <c r="T232" t="n">
-        <v>67.01094691062777</v>
+        <v>51.71092250079126</v>
       </c>
     </row>
     <row r="233">
@@ -17613,19 +17545,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P233" t="n">
-        <v>80.72811473942431</v>
+        <v>80.66495465709515</v>
       </c>
       <c r="Q233" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R233" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>63.79659522778243</v>
+        <v>48.47946786587859</v>
       </c>
       <c r="T233" t="n">
-        <v>63.79659522778243</v>
+        <v>48.47946786587859</v>
       </c>
     </row>
     <row r="234">
@@ -17687,19 +17619,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P234" t="n">
-        <v>79.33002017685395</v>
+        <v>79.26227809507419</v>
       </c>
       <c r="Q234" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R234" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
-        <v>68.15435119615746</v>
+        <v>52.84293301209592</v>
       </c>
       <c r="T234" t="n">
-        <v>68.15435119615746</v>
+        <v>52.84293301209592</v>
       </c>
     </row>
     <row r="235">
@@ -17761,19 +17693,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P235" t="n">
-        <v>70.00938975971818</v>
+        <v>69.91110101493446</v>
       </c>
       <c r="Q235" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R235" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>56.40358635723823</v>
+        <v>41.04712220557946</v>
       </c>
       <c r="T235" t="n">
-        <v>56.40358635723823</v>
+        <v>41.04712220557946</v>
       </c>
     </row>
     <row r="236">
@@ -17835,19 +17767,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P236" t="n">
-        <v>69.91618345554681</v>
+        <v>69.81758924413306</v>
       </c>
       <c r="Q236" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R236" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>56.33929932358132</v>
+        <v>40.98249311288121</v>
       </c>
       <c r="T236" t="n">
-        <v>56.33929932358132</v>
+        <v>40.98249311288121</v>
       </c>
     </row>
     <row r="237">
@@ -17909,19 +17841,19 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P237" t="n">
-        <v>66.18793128869251</v>
+        <v>66.07711841207717</v>
       </c>
       <c r="Q237" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R237" t="n">
-        <v>2.087091386303985</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>59.08987945053368</v>
+        <v>43.7302309416422</v>
       </c>
       <c r="T237" t="n">
-        <v>59.08987945053368</v>
+        <v>43.7302309416422</v>
       </c>
     </row>
     <row r="238">
@@ -17985,7 +17917,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P238" t="n">
-        <v>113.0435074140034</v>
+        <v>113.0764819565611</v>
       </c>
       <c r="Q238" t="n">
         <v>8.481819999999999</v>
@@ -17994,10 +17926,10 @@
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>94.13797625024773</v>
+        <v>80.78411158804369</v>
       </c>
       <c r="T238" t="n">
-        <v>94.13797625024773</v>
+        <v>80.78411158804369</v>
       </c>
     </row>
     <row r="239">
@@ -18059,7 +17991,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P239" t="n">
-        <v>112.78424034286</v>
+        <v>112.8165594472138</v>
       </c>
       <c r="Q239" t="n">
         <v>-9.155140000000017</v>
@@ -18068,10 +18000,10 @@
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>81.79444045315108</v>
+        <v>68.41498127649291</v>
       </c>
       <c r="T239" t="n">
-        <v>81.79444045315108</v>
+        <v>68.41498127649291</v>
       </c>
     </row>
     <row r="240">
@@ -18133,7 +18065,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P240" t="n">
-        <v>111.4879049871429</v>
+        <v>111.5169469004775</v>
       </c>
       <c r="Q240" t="n">
         <v>5.174889999999976</v>
@@ -18142,10 +18074,10 @@
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>90.78414961199076</v>
+        <v>77.42073584906413</v>
       </c>
       <c r="T240" t="n">
-        <v>90.78414961199076</v>
+        <v>77.42073584906413</v>
       </c>
     </row>
     <row r="241">
@@ -18207,7 +18139,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P241" t="n">
-        <v>108.8952342757087</v>
+        <v>108.9177218070049</v>
       </c>
       <c r="Q241" t="n">
         <v>-1.438970000000012</v>
@@ -18216,10 +18148,10 @@
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>84.43414405205365</v>
+        <v>71.05326654076141</v>
       </c>
       <c r="T241" t="n">
-        <v>84.43414405205365</v>
+        <v>71.05326654076141</v>
       </c>
     </row>
     <row r="242">
@@ -18281,7 +18213,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P242" t="n">
-        <v>106.950731242133</v>
+        <v>106.9683029869004</v>
       </c>
       <c r="Q242" t="n">
         <v>1.867959999999982</v>
@@ -18290,10 +18222,10 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>85.37384860341717</v>
+        <v>71.99148763456057</v>
       </c>
       <c r="T242" t="n">
-        <v>85.37384860341717</v>
+        <v>71.99148763456057</v>
       </c>
     </row>
     <row r="243">
@@ -18355,7 +18287,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P243" t="n">
-        <v>106.6914641709896</v>
+        <v>106.7083804775532</v>
       </c>
       <c r="Q243" t="n">
         <v>-3.643590000000017</v>
@@ -18364,10 +18296,10 @@
         <v>0</v>
       </c>
       <c r="S243" t="n">
-        <v>81.39355226425121</v>
+        <v>68.00263116638158</v>
       </c>
       <c r="T243" t="n">
-        <v>81.39355226425121</v>
+        <v>68.00263116638158</v>
       </c>
     </row>
     <row r="244">
@@ -18429,7 +18361,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P244" t="n">
-        <v>106.6136840496466</v>
+        <v>106.630403724749</v>
       </c>
       <c r="Q244" t="n">
         <v>-4.745900000000006</v>
@@ -18438,10 +18370,10 @@
         <v>0</v>
       </c>
       <c r="S244" t="n">
-        <v>80.57961061058919</v>
+        <v>67.18689576426297</v>
       </c>
       <c r="T244" t="n">
-        <v>80.57961061058919</v>
+        <v>67.18689576426297</v>
       </c>
     </row>
     <row r="245">
@@ -18503,7 +18435,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P245" t="n">
-        <v>104.0210133382124</v>
+        <v>104.0311786312764</v>
       </c>
       <c r="Q245" t="n">
         <v>-1.438970000000012</v>
@@ -18512,10 +18444,10 @@
         <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>81.07225551623171</v>
+        <v>67.67601414599169</v>
       </c>
       <c r="T245" t="n">
-        <v>81.07225551623171</v>
+        <v>67.67601414599169</v>
       </c>
     </row>
     <row r="246">
@@ -18577,7 +18509,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P246" t="n">
-        <v>97.53933655962685</v>
+        <v>97.53311589759483</v>
       </c>
       <c r="Q246" t="n">
         <v>-1.438970000000012</v>
@@ -18586,10 +18518,10 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>76.60165905902164</v>
+        <v>63.18498702528728</v>
       </c>
       <c r="T246" t="n">
-        <v>76.60165905902164</v>
+        <v>63.18498702528728</v>
       </c>
     </row>
     <row r="247">
@@ -18651,7 +18583,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P247" t="n">
-        <v>97.28006948848342</v>
+        <v>97.27319338824756</v>
       </c>
       <c r="Q247" t="n">
         <v>-9.155140000000017</v>
@@ -18660,10 +18592,10 @@
         <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>71.10077372750463</v>
+        <v>57.67244440376796</v>
       </c>
       <c r="T247" t="n">
-        <v>71.10077372750463</v>
+        <v>57.67244440376796</v>
       </c>
     </row>
     <row r="248">
@@ -18725,7 +18657,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P248" t="n">
-        <v>89.50205735418081</v>
+        <v>89.4755181078297</v>
       </c>
       <c r="Q248" t="n">
         <v>-9.155140000000017</v>
@@ -18734,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>65.73605797885257</v>
+        <v>52.28321185892267</v>
       </c>
       <c r="T248" t="n">
-        <v>65.73605797885257</v>
+        <v>52.28321185892267</v>
       </c>
     </row>
     <row r="249">
@@ -18799,7 +18731,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P249" t="n">
-        <v>88.85388967632225</v>
+        <v>88.82571183446154</v>
       </c>
       <c r="Q249" t="n">
         <v>-4.745900000000006</v>
@@ -18808,10 +18740,10 @@
         <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>68.33017631783363</v>
+        <v>54.88148145353288</v>
       </c>
       <c r="T249" t="n">
-        <v>68.33017631783363</v>
+        <v>54.88148145353288</v>
       </c>
     </row>
     <row r="250">
@@ -18873,7 +18805,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P250" t="n">
-        <v>83.66854825345385</v>
+        <v>83.62726164751631</v>
       </c>
       <c r="Q250" t="n">
         <v>11.78874999999999</v>
@@ -18882,10 +18814,10 @@
         <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>76.15811659469833</v>
+        <v>62.71630590702179</v>
       </c>
       <c r="T250" t="n">
-        <v>76.15811659469833</v>
+        <v>62.71630590702179</v>
       </c>
     </row>
     <row r="251">
@@ -18947,7 +18879,7 @@
         <v>0.0007329099433618525</v>
       </c>
       <c r="P251" t="n">
-        <v>77.18687147486833</v>
+        <v>77.12919891383476</v>
       </c>
       <c r="Q251" t="n">
         <v>-6.950520000000012</v>
@@ -18956,10 +18888,10 @@
         <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>58.7625137025045</v>
+        <v>45.27394648292462</v>
       </c>
       <c r="T251" t="n">
-        <v>58.7625137025045</v>
+        <v>45.27394648292462</v>
       </c>
     </row>
     <row r="252">
@@ -19023,7 +18955,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P252" t="n">
-        <v>95.92558365584971</v>
+        <v>95.93438868172906</v>
       </c>
       <c r="Q252" t="n">
         <v>1.867959999999982</v>
@@ -19032,10 +18964,10 @@
         <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>78.16125622286468</v>
+        <v>64.36558274213768</v>
       </c>
       <c r="T252" t="n">
-        <v>78.16125622286468</v>
+        <v>64.36558274213768</v>
       </c>
     </row>
     <row r="253">
@@ -19097,7 +19029,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P253" t="n">
-        <v>95.75721593882434</v>
+        <v>95.76638481610729</v>
       </c>
       <c r="Q253" t="n">
         <v>6.277199999999993</v>
@@ -19106,10 +19038,10 @@
         <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>81.08630621400049</v>
+        <v>67.29684199361809</v>
       </c>
       <c r="T253" t="n">
-        <v>81.08630621400049</v>
+        <v>67.29684199361809</v>
       </c>
     </row>
     <row r="254">
@@ -19171,7 +19103,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P254" t="n">
-        <v>91.54802301319035</v>
+        <v>91.5662881755632</v>
       </c>
       <c r="Q254" t="n">
         <v>-0.3366600000000091</v>
@@ -19180,10 +19112,10 @@
         <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>73.62133939779103</v>
+        <v>59.82295715359139</v>
       </c>
       <c r="T254" t="n">
-        <v>73.62133939779103</v>
+        <v>59.82295715359139</v>
       </c>
     </row>
     <row r="255">
@@ -19245,7 +19177,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P255" t="n">
-        <v>89.44342655037333</v>
+        <v>89.46623985529116</v>
       </c>
       <c r="Q255" t="n">
         <v>-2.541280000000015</v>
@@ -19254,10 +19186,10 @@
         <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>70.64915048586181</v>
+        <v>56.84785781024819</v>
       </c>
       <c r="T255" t="n">
-        <v>70.64915048586181</v>
+        <v>56.84785781024819</v>
       </c>
     </row>
     <row r="256">
@@ -19319,7 +19251,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P256" t="n">
-        <v>89.39291623526573</v>
+        <v>89.41583869560463</v>
       </c>
       <c r="Q256" t="n">
         <v>5.174889999999976</v>
@@ -19328,10 +19260,10 @@
         <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>75.93637356102055</v>
+        <v>62.14592543037925</v>
       </c>
       <c r="T256" t="n">
-        <v>75.93637356102055</v>
+        <v>62.14592543037925</v>
       </c>
     </row>
     <row r="257">
@@ -19393,7 +19325,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P257" t="n">
-        <v>87.70923906501213</v>
+        <v>87.735800039387</v>
       </c>
       <c r="Q257" t="n">
         <v>4.072579999999988</v>
@@ -19402,10 +19334,10 @@
         <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>74.01479912918249</v>
+        <v>60.22295180170681</v>
       </c>
       <c r="T257" t="n">
-        <v>74.01479912918249</v>
+        <v>60.22295180170681</v>
       </c>
     </row>
     <row r="258">
@@ -19467,7 +19399,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P258" t="n">
-        <v>87.28831977244872</v>
+        <v>87.31579037533258</v>
       </c>
       <c r="Q258" t="n">
         <v>-5.848210000000009</v>
@@ -19476,10 +19408,10 @@
         <v>0</v>
       </c>
       <c r="S258" t="n">
-        <v>66.88182867968722</v>
+        <v>53.07608147367478</v>
       </c>
       <c r="T258" t="n">
-        <v>66.88182867968722</v>
+        <v>53.07608147367478</v>
       </c>
     </row>
     <row r="259">
@@ -19541,7 +19473,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P259" t="n">
-        <v>84.34188472450492</v>
+        <v>84.37572272695172</v>
       </c>
       <c r="Q259" t="n">
         <v>-3.643590000000017</v>
@@ -19550,10 +19482,10 @@
         <v>0</v>
       </c>
       <c r="S259" t="n">
-        <v>66.37017778462878</v>
+        <v>52.56778916101108</v>
       </c>
       <c r="T259" t="n">
-        <v>66.37017778462878</v>
+        <v>52.56778916101108</v>
       </c>
     </row>
     <row r="260">
@@ -19615,7 +19547,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P260" t="n">
-        <v>84.17351700747956</v>
+        <v>84.20771886132997</v>
       </c>
       <c r="Q260" t="n">
         <v>-4.745900000000006</v>
@@ -19624,10 +19556,10 @@
         <v>0</v>
       </c>
       <c r="S260" t="n">
-        <v>65.49375529488702</v>
+        <v>51.6898330291407</v>
       </c>
       <c r="T260" t="n">
-        <v>65.49375529488702</v>
+        <v>51.6898330291407</v>
       </c>
     </row>
     <row r="261">
@@ -19689,7 +19621,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P261" t="n">
-        <v>83.75259771491616</v>
+        <v>83.78770919727555</v>
       </c>
       <c r="Q261" t="n">
         <v>-8.052830000000014</v>
@@ -19698,10 +19630,10 @@
         <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>62.92255182244483</v>
+        <v>49.11402116112963</v>
       </c>
       <c r="T261" t="n">
-        <v>62.92255182244483</v>
+        <v>49.11402116112963</v>
       </c>
     </row>
     <row r="262">
@@ -19763,7 +19695,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P262" t="n">
-        <v>82.06892054466255</v>
+        <v>82.10767054105791</v>
       </c>
       <c r="Q262" t="n">
         <v>2.970269999999999</v>
@@ -19772,10 +19704,10 @@
         <v>0</v>
       </c>
       <c r="S262" t="n">
-        <v>69.36421684853745</v>
+        <v>55.57132137582897</v>
       </c>
       <c r="T262" t="n">
-        <v>69.36421684853745</v>
+        <v>55.57132137582897</v>
       </c>
     </row>
     <row r="263">
@@ -19837,7 +19769,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P263" t="n">
-        <v>77.85972761902855</v>
+        <v>77.90757390051382</v>
       </c>
       <c r="Q263" t="n">
         <v>-12.46207000000001</v>
@@ -19846,10 +19778,10 @@
         <v>0</v>
       </c>
       <c r="S263" t="n">
-        <v>55.81689406292385</v>
+        <v>42.00269192244095</v>
       </c>
       <c r="T263" t="n">
-        <v>55.81689406292385</v>
+        <v>42.00269192244095</v>
       </c>
     </row>
     <row r="264">
@@ -19911,7 +19843,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P264" t="n">
-        <v>69.44134176776053</v>
+        <v>69.50738061942565</v>
       </c>
       <c r="Q264" t="n">
         <v>4.072579999999988</v>
@@ -19920,10 +19852,10 @@
         <v>0</v>
       </c>
       <c r="S264" t="n">
-        <v>61.41491182724386</v>
+        <v>47.62468531248192</v>
       </c>
       <c r="T264" t="n">
-        <v>61.41491182724386</v>
+        <v>47.62468531248192</v>
       </c>
     </row>
     <row r="265">
@@ -19985,7 +19917,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P265" t="n">
-        <v>49.01922708048703</v>
+        <v>49.12939918539485</v>
       </c>
       <c r="Q265" t="n">
         <v>2.970269999999999</v>
@@ -20055,7 +19987,7 @@
         <v>0.001382060337697549</v>
       </c>
       <c r="P266" t="n">
-        <v>46.49371132510663</v>
+        <v>46.6093412010684</v>
       </c>
       <c r="Q266" t="n">
         <v>6.277199999999993</v>
@@ -20127,7 +20059,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P267" t="n">
-        <v>107.2407022404909</v>
+        <v>107.2250547059173</v>
       </c>
       <c r="Q267" t="n">
         <v>-1.438970000000012</v>
@@ -20136,10 +20068,10 @@
         <v>0</v>
       </c>
       <c r="S267" t="n">
-        <v>83.46695488550851</v>
+        <v>69.88340805079859</v>
       </c>
       <c r="T267" t="n">
-        <v>83.46695488550851</v>
+        <v>69.88340805079859</v>
       </c>
     </row>
     <row r="268">
@@ -20201,7 +20133,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P268" t="n">
-        <v>106.8137765064941</v>
+        <v>106.7990515806622</v>
       </c>
       <c r="Q268" t="n">
         <v>-10.25745000000001</v>
@@ -20210,10 +20142,10 @@
         <v>0</v>
       </c>
       <c r="S268" t="n">
-        <v>77.09013611903869</v>
+        <v>63.49423851920604</v>
       </c>
       <c r="T268" t="n">
-        <v>77.09013611903869</v>
+        <v>63.49423851920604</v>
       </c>
     </row>
     <row r="269">
@@ -20275,7 +20207,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P269" t="n">
-        <v>106.7283913596947</v>
+        <v>106.7138509556112</v>
       </c>
       <c r="Q269" t="n">
         <v>1.867959999999982</v>
@@ -20284,10 +20216,10 @@
         <v>0</v>
       </c>
       <c r="S269" t="n">
-        <v>85.39448301755623</v>
+        <v>71.81562737893157</v>
       </c>
       <c r="T269" t="n">
-        <v>85.39448301755623</v>
+        <v>71.81562737893157</v>
       </c>
     </row>
     <row r="270">
@@ -20349,7 +20281,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P270" t="n">
-        <v>102.4591340197262</v>
+        <v>102.4538197030596</v>
       </c>
       <c r="Q270" t="n">
         <v>-4.745900000000006</v>
@@ -20358,10 +20290,10 @@
         <v>0</v>
       </c>
       <c r="S270" t="n">
-        <v>77.88808806984609</v>
+        <v>64.30031973659806</v>
       </c>
       <c r="T270" t="n">
-        <v>77.88808806984609</v>
+        <v>64.30031973659806</v>
       </c>
     </row>
     <row r="271">
@@ -20423,7 +20355,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P271" t="n">
-        <v>101.6052825517325</v>
+        <v>101.6018134525492</v>
       </c>
       <c r="Q271" t="n">
         <v>-4.745900000000006</v>
@@ -20432,10 +20364,10 @@
         <v>0</v>
       </c>
       <c r="S271" t="n">
-        <v>77.29916247571465</v>
+        <v>63.71146990013554</v>
       </c>
       <c r="T271" t="n">
-        <v>77.29916247571465</v>
+        <v>63.71146990013554</v>
       </c>
     </row>
     <row r="272">
@@ -20497,7 +20429,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P272" t="n">
-        <v>100.7514310837388</v>
+        <v>100.7498072020389</v>
       </c>
       <c r="Q272" t="n">
         <v>-5.848210000000009</v>
@@ -20506,10 +20438,10 @@
         <v>0</v>
       </c>
       <c r="S272" t="n">
-        <v>75.94994238540774</v>
+        <v>62.36077698700286</v>
       </c>
       <c r="T272" t="n">
-        <v>75.94994238540774</v>
+        <v>62.36077698700286</v>
       </c>
     </row>
     <row r="273">
@@ -20571,7 +20503,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P273" t="n">
-        <v>100.4952756433407</v>
+        <v>100.4942053268858</v>
       </c>
       <c r="Q273" t="n">
         <v>5.174889999999976</v>
@@ -20580,10 +20512,10 @@
         <v>0</v>
       </c>
       <c r="S273" t="n">
-        <v>83.37620966892347</v>
+        <v>69.80255280276572</v>
       </c>
       <c r="T273" t="n">
-        <v>83.37620966892347</v>
+        <v>69.80255280276572</v>
       </c>
     </row>
     <row r="274">
@@ -20645,7 +20577,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P274" t="n">
-        <v>98.78757270735326</v>
+        <v>98.79019282586519</v>
       </c>
       <c r="Q274" t="n">
         <v>-10.25745000000001</v>
@@ -20654,10 +20586,10 @@
         <v>0</v>
       </c>
       <c r="S274" t="n">
-        <v>71.55423553420341</v>
+        <v>57.95905005645844</v>
       </c>
       <c r="T274" t="n">
-        <v>71.55423553420341</v>
+        <v>57.95905005645844</v>
       </c>
     </row>
     <row r="275">
@@ -20719,7 +20651,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P275" t="n">
-        <v>97.50679550536272</v>
+        <v>97.51218345009971</v>
       </c>
       <c r="Q275" t="n">
         <v>-0.3366600000000091</v>
@@ -20728,10 +20660,10 @@
         <v>0</v>
       </c>
       <c r="S275" t="n">
-        <v>77.51349760858595</v>
+        <v>63.93236299179613</v>
       </c>
       <c r="T275" t="n">
-        <v>77.51349760858595</v>
+        <v>63.93236299179613</v>
       </c>
     </row>
     <row r="276">
@@ -20793,7 +20725,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P276" t="n">
-        <v>94.09138963338791</v>
+        <v>94.10415844805844</v>
       </c>
       <c r="Q276" t="n">
         <v>4.072579999999988</v>
@@ -20802,10 +20734,10 @@
         <v>0</v>
       </c>
       <c r="S276" t="n">
-        <v>78.19897321676235</v>
+        <v>64.62433595262674</v>
       </c>
       <c r="T276" t="n">
-        <v>78.19897321676235</v>
+        <v>64.62433595262674</v>
       </c>
     </row>
     <row r="277">
@@ -20867,7 +20799,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P277" t="n">
-        <v>93.92061933978917</v>
+        <v>93.93375719795638</v>
       </c>
       <c r="Q277" t="n">
         <v>6.277199999999993</v>
@@ -20876,10 +20808,10 @@
         <v>0</v>
       </c>
       <c r="S277" t="n">
-        <v>79.60177709028711</v>
+        <v>66.03025213867457</v>
       </c>
       <c r="T277" t="n">
-        <v>79.60177709028711</v>
+        <v>66.03025213867457</v>
       </c>
     </row>
     <row r="278">
@@ -20941,7 +20873,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P278" t="n">
-        <v>93.74984904619043</v>
+        <v>93.76335594785431</v>
       </c>
       <c r="Q278" t="n">
         <v>6.277199999999993</v>
@@ -20950,10 +20882,10 @@
         <v>0</v>
       </c>
       <c r="S278" t="n">
-        <v>79.48399197146084</v>
+        <v>65.91248217138205</v>
       </c>
       <c r="T278" t="n">
-        <v>79.48399197146084</v>
+        <v>65.91248217138205</v>
       </c>
     </row>
     <row r="279">
@@ -21015,7 +20947,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P279" t="n">
-        <v>92.04214611020302</v>
+        <v>92.05934344683368</v>
       </c>
       <c r="Q279" t="n">
         <v>-8.052830000000014</v>
@@ -21024,10 +20956,10 @@
         <v>0</v>
       </c>
       <c r="S279" t="n">
-        <v>68.42231233291631</v>
+        <v>54.83082250174493</v>
       </c>
       <c r="T279" t="n">
-        <v>68.42231233291631</v>
+        <v>54.83082250174493</v>
       </c>
     </row>
     <row r="280">
@@ -21089,7 +21021,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P280" t="n">
-        <v>86.91903730224081</v>
+        <v>86.94730594377177</v>
       </c>
       <c r="Q280" t="n">
         <v>-0.3366600000000091</v>
@@ -21098,10 +21030,10 @@
         <v>0</v>
       </c>
       <c r="S280" t="n">
-        <v>70.21082024135644</v>
+        <v>56.630625019661</v>
       </c>
       <c r="T280" t="n">
-        <v>70.21082024135644</v>
+        <v>56.630625019661</v>
       </c>
     </row>
     <row r="281">
@@ -21163,7 +21095,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P281" t="n">
-        <v>85.21133436625341</v>
+        <v>85.24329344275112</v>
       </c>
       <c r="Q281" t="n">
         <v>1.867959999999982</v>
@@ -21172,10 +21104,10 @@
         <v>0</v>
       </c>
       <c r="S281" t="n">
-        <v>70.55355804544466</v>
+        <v>56.9766115000763</v>
       </c>
       <c r="T281" t="n">
-        <v>70.55355804544466</v>
+        <v>56.9766115000763</v>
       </c>
     </row>
     <row r="282">
@@ -21237,7 +21169,7 @@
         <v>0.001021207191094621</v>
       </c>
       <c r="P282" t="n">
-        <v>84.3574828982597</v>
+        <v>84.39128719224081</v>
       </c>
       <c r="Q282" t="n">
         <v>-1.438970000000012</v>
@@ -21246,10 +21178,10 @@
         <v>0</v>
       </c>
       <c r="S282" t="n">
-        <v>67.68374896278669</v>
+        <v>54.10223243360331</v>
       </c>
       <c r="T282" t="n">
-        <v>67.68374896278669</v>
+        <v>54.10223243360331</v>
       </c>
     </row>
     <row r="283">
@@ -21313,7 +21245,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P283" t="n">
-        <v>109.6870876177443</v>
+        <v>109.711576988032</v>
       </c>
       <c r="Q283" t="n">
         <v>2.970269999999999</v>
@@ -21322,10 +21254,10 @@
         <v>0</v>
       </c>
       <c r="S283" t="n">
-        <v>88.12077190552658</v>
+        <v>74.64929854711295</v>
       </c>
       <c r="T283" t="n">
-        <v>88.12077190552658</v>
+        <v>74.64929854711295</v>
       </c>
     </row>
     <row r="284">
@@ -21387,7 +21319,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P284" t="n">
-        <v>108.39751022003</v>
+        <v>108.4187394837043</v>
       </c>
       <c r="Q284" t="n">
         <v>0.7656499999999937</v>
@@ -21396,10 +21328,10 @@
         <v>0</v>
       </c>
       <c r="S284" t="n">
-        <v>85.71072477719336</v>
+        <v>72.23208942661131</v>
       </c>
       <c r="T284" t="n">
-        <v>85.71072477719336</v>
+        <v>72.23208942661131</v>
       </c>
     </row>
     <row r="285">
@@ -21461,7 +21393,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P285" t="n">
-        <v>104.5287780268872</v>
+        <v>104.5402269707212</v>
       </c>
       <c r="Q285" t="n">
         <v>-6.950520000000012</v>
@@ -21470,10 +21402,10 @@
         <v>0</v>
       </c>
       <c r="S285" t="n">
-        <v>77.7202888960182</v>
+        <v>64.21861898843625</v>
       </c>
       <c r="T285" t="n">
-        <v>77.7202888960182</v>
+        <v>64.21861898843625</v>
       </c>
     </row>
     <row r="286">
@@ -21535,7 +21467,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P286" t="n">
-        <v>98.08089103831576</v>
+        <v>98.07603944908278</v>
       </c>
       <c r="Q286" t="n">
         <v>6.277199999999993</v>
@@ -21544,10 +21476,10 @@
         <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>82.39653217021352</v>
+        <v>68.89312107267168</v>
       </c>
       <c r="T286" t="n">
-        <v>82.39653217021352</v>
+        <v>68.89312107267168</v>
       </c>
     </row>
     <row r="287">
@@ -21609,7 +21541,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P287" t="n">
-        <v>97.95193329854432</v>
+        <v>97.94675569865001</v>
       </c>
       <c r="Q287" t="n">
         <v>1.867959999999982</v>
@@ -21618,10 +21550,10 @@
         <v>0</v>
       </c>
       <c r="S287" t="n">
-        <v>79.26640837191322</v>
+        <v>65.75639646927488</v>
       </c>
       <c r="T287" t="n">
-        <v>79.26640837191322</v>
+        <v>65.75639646927488</v>
       </c>
     </row>
     <row r="288">
@@ -21683,7 +21615,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P288" t="n">
-        <v>91.50404630997289</v>
+        <v>91.48256817701157</v>
       </c>
       <c r="Q288" t="n">
         <v>-4.745900000000006</v>
@@ -21692,10 +21624,10 @@
         <v>0</v>
       </c>
       <c r="S288" t="n">
-        <v>70.25735071494925</v>
+        <v>56.71772317344738</v>
       </c>
       <c r="T288" t="n">
-        <v>70.25735071494925</v>
+        <v>56.71772317344738</v>
       </c>
     </row>
     <row r="289">
@@ -21757,7 +21689,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P289" t="n">
-        <v>88.92489151454433</v>
+        <v>88.8968931683562</v>
       </c>
       <c r="Q289" t="n">
         <v>0.7656499999999937</v>
@@ -21766,10 +21698,10 @@
         <v>0</v>
       </c>
       <c r="S289" t="n">
-        <v>72.27990692386247</v>
+        <v>58.73989262247558</v>
       </c>
       <c r="T289" t="n">
-        <v>72.27990692386247</v>
+        <v>58.73989262247558</v>
       </c>
     </row>
     <row r="290">
@@ -21831,7 +21763,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P290" t="n">
-        <v>86.34573671911576</v>
+        <v>86.31121815970081</v>
       </c>
       <c r="Q290" t="n">
         <v>2.970269999999999</v>
@@ -21840,10 +21772,10 @@
         <v>0</v>
       </c>
       <c r="S290" t="n">
-        <v>72.02157964424914</v>
+        <v>58.47653284149329</v>
       </c>
       <c r="T290" t="n">
-        <v>72.02157964424914</v>
+        <v>58.47653284149329</v>
       </c>
     </row>
     <row r="291">
@@ -21905,7 +21837,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P291" t="n">
-        <v>86.0878212395729</v>
+        <v>86.05265065883529</v>
       </c>
       <c r="Q291" t="n">
         <v>-13.56438000000001</v>
@@ -21914,10 +21846,10 @@
         <v>0</v>
       </c>
       <c r="S291" t="n">
-        <v>60.43927057441997</v>
+        <v>46.8701820980086</v>
       </c>
       <c r="T291" t="n">
-        <v>60.43927057441997</v>
+        <v>46.8701820980086</v>
       </c>
     </row>
     <row r="292">
@@ -21979,7 +21911,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P292" t="n">
-        <v>86.01044659571005</v>
+        <v>85.97508040857562</v>
       </c>
       <c r="Q292" t="n">
         <v>1.867959999999982</v>
@@ -21988,10 +21920,10 @@
         <v>0</v>
       </c>
       <c r="S292" t="n">
-        <v>71.03002603271825</v>
+        <v>57.48237379336118</v>
       </c>
       <c r="T292" t="n">
-        <v>71.03002603271825</v>
+        <v>57.48237379336118</v>
       </c>
     </row>
     <row r="293">
@@ -22053,7 +21985,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P293" t="n">
-        <v>82.14171440256719</v>
+        <v>82.09656789559256</v>
       </c>
       <c r="Q293" t="n">
         <v>-5.848210000000009</v>
@@ -22062,10 +21994,10 @@
         <v>0</v>
       </c>
       <c r="S293" t="n">
-        <v>63.03959015154312</v>
+        <v>49.46890335518613</v>
       </c>
       <c r="T293" t="n">
-        <v>63.03959015154312</v>
+        <v>49.46890335518613</v>
       </c>
     </row>
     <row r="294">
@@ -22127,7 +22059,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P294" t="n">
-        <v>79.56255960713862</v>
+        <v>79.51089288693719</v>
       </c>
       <c r="Q294" t="n">
         <v>-8.052830000000014</v>
@@ -22136,10 +22068,10 @@
         <v>0</v>
       </c>
       <c r="S294" t="n">
-        <v>59.74008488722773</v>
+        <v>46.15817126752319</v>
       </c>
       <c r="T294" t="n">
-        <v>59.74008488722773</v>
+        <v>46.15817126752319</v>
       </c>
     </row>
     <row r="295">
@@ -22201,7 +22133,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P295" t="n">
-        <v>58.92932124371007</v>
+        <v>58.82549281769417</v>
       </c>
       <c r="Q295" t="n">
         <v>1.867959999999982</v>
@@ -22210,10 +22142,10 @@
         <v>0</v>
       </c>
       <c r="S295" t="n">
-        <v>52.35140517709252</v>
+        <v>38.71839148297374</v>
       </c>
       <c r="T295" t="n">
-        <v>52.35140517709252</v>
+        <v>38.71839148297374</v>
       </c>
     </row>
     <row r="296">
@@ -22275,7 +22207,7 @@
         <v>0.0008974260723941122</v>
       </c>
       <c r="P296" t="n">
-        <v>48.20929569775986</v>
+        <v>48.07836659035782</v>
       </c>
       <c r="Q296" t="n">
         <v>-6.950520000000012</v>
